--- a/data/物流账单.xlsx
+++ b/data/物流账单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sicheng1806\workspace\project\logirecon\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FF97CF-0ACD-4A88-B3DB-DD5C485AF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898DC9E9-2CE8-4EB5-9BF6-28DC0AD673FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{E98E0870-61F2-43AD-B3AC-7EBE6B59DB5C}"/>
+    <workbookView xWindow="3670" yWindow="3140" windowWidth="17530" windowHeight="11170" firstSheet="4" activeTab="7" xr2:uid="{E98E0870-61F2-43AD-B3AC-7EBE6B59DB5C}"/>
   </bookViews>
   <sheets>
     <sheet name="万邦2604" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="嘀嗒嘀4月账单" sheetId="8" r:id="rId5"/>
     <sheet name="积米2605" sheetId="9" r:id="rId6"/>
     <sheet name="京奕达2605" sheetId="10" r:id="rId7"/>
+    <sheet name="万邦2605" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">天盛报关费2604!$A$7:$Q$28</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="563">
   <si>
     <t>天盛供应链（广州）有限公司</t>
   </si>
@@ -1441,6 +1442,315 @@
   </si>
   <si>
     <t>公司账户:    755983713510088  （RMB）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202606060012 </t>
+  </si>
+  <si>
+    <t>WB2605088524</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>美国海派限时达-普船</t>
+  </si>
+  <si>
+    <t>CN6339</t>
+  </si>
+  <si>
+    <t>16.90/KG</t>
+  </si>
+  <si>
+    <t>WB2605087115</t>
+  </si>
+  <si>
+    <t>FBA19CS2J6FM</t>
+  </si>
+  <si>
+    <t>YOW1</t>
+  </si>
+  <si>
+    <t>6.60/KG</t>
+  </si>
+  <si>
+    <t>2026/05/10</t>
+  </si>
+  <si>
+    <t>WB2605089744</t>
+  </si>
+  <si>
+    <t>FBA19CVZRY66</t>
+  </si>
+  <si>
+    <t>WB2605084875</t>
+  </si>
+  <si>
+    <t>FBA19CVVZN2V</t>
+  </si>
+  <si>
+    <t>美西拆柜专线-快船</t>
+  </si>
+  <si>
+    <t>9.40/KG</t>
+  </si>
+  <si>
+    <t>WB2605087434</t>
+  </si>
+  <si>
+    <t>FBA19CVTGBRQ</t>
+  </si>
+  <si>
+    <t>WB2605084974</t>
+  </si>
+  <si>
+    <t>FBA19CKXTVFC</t>
+  </si>
+  <si>
+    <t>QXY8</t>
+  </si>
+  <si>
+    <t>4.60/KG</t>
+  </si>
+  <si>
+    <t>WB2605081113</t>
+  </si>
+  <si>
+    <t>FBA19CVTVQS7</t>
+  </si>
+  <si>
+    <t>WB2605084491</t>
+  </si>
+  <si>
+    <t>FBA19CSKJ9TY</t>
+  </si>
+  <si>
+    <t>WB2605089861</t>
+  </si>
+  <si>
+    <t>FBA19CJWGL14,FBA19CSDPQT6</t>
+  </si>
+  <si>
+    <t>4.50/KG</t>
+  </si>
+  <si>
+    <t>WB2605088504</t>
+  </si>
+  <si>
+    <t>FBA19CKRNYM2</t>
+  </si>
+  <si>
+    <t>2026/05/14</t>
+  </si>
+  <si>
+    <t>WB2605135083</t>
+  </si>
+  <si>
+    <t>FBA15LQT5NPH</t>
+  </si>
+  <si>
+    <t>英国海卡专线-按方</t>
+  </si>
+  <si>
+    <t>LBA4-DN110GU</t>
+  </si>
+  <si>
+    <t>780.00/立方</t>
+  </si>
+  <si>
+    <t>清关费</t>
+  </si>
+  <si>
+    <t>0.10/票</t>
+  </si>
+  <si>
+    <t>关税</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>待补</t>
+  </si>
+  <si>
+    <t>WB2605149645</t>
+  </si>
+  <si>
+    <t>FBA19CXL7FRP,FBA19CXM6Z07</t>
+  </si>
+  <si>
+    <t>4.95/KG</t>
+  </si>
+  <si>
+    <t>2026/05/16</t>
+  </si>
+  <si>
+    <t>WB2605146378</t>
+  </si>
+  <si>
+    <t>FBA19CY3DWCX,FBA19CY3S27T,FBA19D384MDF</t>
+  </si>
+  <si>
+    <t>4.25/KG</t>
+  </si>
+  <si>
+    <t>WB2605146909</t>
+  </si>
+  <si>
+    <t>FBA19D93KMHJ,FBA19D94S4L0</t>
+  </si>
+  <si>
+    <t>WB2605145920</t>
+  </si>
+  <si>
+    <t>FBA19CYBYB8S,FBA19D0YVFRX,FBA19D4HMDZM</t>
+  </si>
+  <si>
+    <t>4.35/KG</t>
+  </si>
+  <si>
+    <t>2026/05/17</t>
+  </si>
+  <si>
+    <t>WB2605156846</t>
+  </si>
+  <si>
+    <t>FBA19DCQDFHJ</t>
+  </si>
+  <si>
+    <t>美中拆柜专线-普船</t>
+  </si>
+  <si>
+    <t>SAT4</t>
+  </si>
+  <si>
+    <t>5.90/KG</t>
+  </si>
+  <si>
+    <t>WB2605153991</t>
+  </si>
+  <si>
+    <t>FBA19DCSKYDJ</t>
+  </si>
+  <si>
+    <t>美东拆柜专线-普船</t>
+  </si>
+  <si>
+    <t>HSV1</t>
+  </si>
+  <si>
+    <t>6.30/KG</t>
+  </si>
+  <si>
+    <t>WB2605159087</t>
+  </si>
+  <si>
+    <t>FBA19DCNSFXR</t>
+  </si>
+  <si>
+    <t>JVL1</t>
+  </si>
+  <si>
+    <t>WB2605156368</t>
+  </si>
+  <si>
+    <t>FBA19DCRKGGZ</t>
+  </si>
+  <si>
+    <t>WB2605154584</t>
+  </si>
+  <si>
+    <t>FBA19DCSC490</t>
+  </si>
+  <si>
+    <t>FAT2</t>
+  </si>
+  <si>
+    <t>5.10/KG</t>
+  </si>
+  <si>
+    <t>WB2605218104</t>
+  </si>
+  <si>
+    <t>FBA19DBRV3ML,FBA19DBWHMS4</t>
+  </si>
+  <si>
+    <t>WB2605218948</t>
+  </si>
+  <si>
+    <t>FBA19DCGXCHB</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>WB2605217764</t>
+  </si>
+  <si>
+    <t>FBA19DCLY68K</t>
+  </si>
+  <si>
+    <t>WB2605218910</t>
+  </si>
+  <si>
+    <t>FBA19CYJ3DZ0</t>
+  </si>
+  <si>
+    <t>2026/05/29</t>
+  </si>
+  <si>
+    <t>WB2605282485</t>
+  </si>
+  <si>
+    <t>FBA19F1CKNMZ</t>
+  </si>
+  <si>
+    <t>ABQ2</t>
+  </si>
+  <si>
+    <t>WB2605288179</t>
+  </si>
+  <si>
+    <t>FBA19DZDJ9ZD</t>
+  </si>
+  <si>
+    <t>WB2605281639</t>
+  </si>
+  <si>
+    <t>FBA19DZ91P1W</t>
+  </si>
+  <si>
+    <t>WB2605283672</t>
+  </si>
+  <si>
+    <t>FBA19DZB5TF6</t>
+  </si>
+  <si>
+    <t>WB2605277823</t>
+  </si>
+  <si>
+    <t>FBA19DVRJ4T5</t>
+  </si>
+  <si>
+    <t>WB2605282358</t>
+  </si>
+  <si>
+    <t>FBA19DX51Y1T</t>
+  </si>
+  <si>
+    <t>WB2605286950</t>
+  </si>
+  <si>
+    <t>FBA19DX4J71R</t>
+  </si>
+  <si>
+    <t>WB2605286325</t>
+  </si>
+  <si>
+    <t>FBA19F6GKFQ6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 82891.50</t>
   </si>
 </sst>
 </file>
@@ -2710,255 +3020,12 @@
     <xf numFmtId="178" fontId="46" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="36" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="36" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="47" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="50" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2969,9 +3036,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="4" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="21" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2984,38 +3048,284 @@
     <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="43" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="4" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="4" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="4" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="36" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="36" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="53" fillId="6" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="53" fillId="6" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="43" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3416,6 +3726,95 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>5023</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>6139</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1943100" cy="1447800"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57904A2B-122F-495C-A77F-28E698416A8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5023" y="6139"/>
+          <a:ext cx="1943100" cy="1447800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>34379</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>273807</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1924050" cy="1704975"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9486C473-96F7-408A-AC74-281CD42038DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4174579" y="22365457"/>
+          <a:ext cx="1924050" cy="1704975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -3752,20 +4151,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A1" s="139"/>
-      <c r="B1" s="139"/>
+      <c r="A1" s="164"/>
+      <c r="B1" s="164"/>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="165" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
       <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:14" ht="24.75" customHeight="1">
@@ -3773,14 +4172,14 @@
       <c r="B2" s="27"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
       <c r="M2" s="29"/>
     </row>
     <row r="3" spans="1:14" ht="24.75" customHeight="1">
@@ -3788,58 +4187,58 @@
       <c r="B3" s="27"/>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
-      <c r="E3" s="141" t="s">
+      <c r="E3" s="166" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
+      <c r="L3" s="166"/>
       <c r="M3" s="29"/>
     </row>
     <row r="4" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A4" s="139"/>
-      <c r="B4" s="139"/>
+      <c r="A4" s="164"/>
+      <c r="B4" s="164"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="141"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="141"/>
+      <c r="E4" s="166"/>
+      <c r="F4" s="166"/>
+      <c r="G4" s="166"/>
+      <c r="H4" s="166"/>
+      <c r="I4" s="166"/>
+      <c r="J4" s="166"/>
+      <c r="K4" s="166"/>
+      <c r="L4" s="166"/>
       <c r="M4" s="29"/>
     </row>
     <row r="5" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A5" s="139"/>
-      <c r="B5" s="139"/>
+      <c r="A5" s="164"/>
+      <c r="B5" s="164"/>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
       <c r="F5" s="29"/>
       <c r="G5" s="29"/>
       <c r="H5" s="29"/>
-      <c r="I5" s="142"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-      <c r="M5" s="142"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="167"/>
+      <c r="M5" s="167"/>
     </row>
     <row r="6" spans="1:14" ht="24.75" customHeight="1">
       <c r="A6" s="31"/>
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134" t="s">
+      <c r="C6" s="168"/>
+      <c r="D6" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="168"/>
       <c r="F6" s="33"/>
       <c r="G6" s="33"/>
       <c r="H6" s="33"/>
@@ -3851,14 +4250,14 @@
     </row>
     <row r="7" spans="1:14" ht="24.75" customHeight="1">
       <c r="A7" s="31"/>
-      <c r="B7" s="134" t="s">
+      <c r="B7" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134" t="s">
+      <c r="C7" s="168"/>
+      <c r="D7" s="168" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="134"/>
+      <c r="E7" s="168"/>
       <c r="F7" s="33"/>
       <c r="G7" s="33"/>
       <c r="H7" s="33"/>
@@ -3870,14 +4269,14 @@
     </row>
     <row r="8" spans="1:14" ht="24.75" customHeight="1">
       <c r="A8" s="35"/>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="134"/>
-      <c r="D8" s="134" t="s">
+      <c r="C8" s="168"/>
+      <c r="D8" s="168" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="134"/>
+      <c r="E8" s="168"/>
       <c r="F8" s="36"/>
       <c r="G8" s="36"/>
       <c r="H8" s="36"/>
@@ -3888,14 +4287,14 @@
       <c r="M8" s="36"/>
     </row>
     <row r="9" spans="1:14" s="38" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="135" t="s">
+      <c r="C9" s="168"/>
+      <c r="D9" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="135"/>
+      <c r="E9" s="173"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40"/>
       <c r="H9" s="40"/>
@@ -5166,56 +5565,56 @@
       <c r="N43" s="47"/>
     </row>
     <row r="44" spans="2:14" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B44" s="136"/>
-      <c r="C44" s="136"/>
-      <c r="D44" s="136"/>
-      <c r="E44" s="136"/>
-      <c r="F44" s="136"/>
-      <c r="G44" s="136"/>
-      <c r="H44" s="136"/>
-      <c r="I44" s="136"/>
-      <c r="J44" s="136"/>
-      <c r="K44" s="136"/>
-      <c r="L44" s="136"/>
-      <c r="M44" s="136"/>
+      <c r="B44" s="174"/>
+      <c r="C44" s="174"/>
+      <c r="D44" s="174"/>
+      <c r="E44" s="174"/>
+      <c r="F44" s="174"/>
+      <c r="G44" s="174"/>
+      <c r="H44" s="174"/>
+      <c r="I44" s="174"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
+      <c r="L44" s="174"/>
+      <c r="M44" s="174"/>
     </row>
     <row r="45" spans="2:14" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B45" s="137"/>
-      <c r="C45" s="137"/>
-      <c r="D45" s="137"/>
-      <c r="E45" s="137"/>
-      <c r="F45" s="137"/>
-      <c r="G45" s="137"/>
-      <c r="H45" s="137"/>
-      <c r="I45" s="137"/>
-      <c r="J45" s="137"/>
-      <c r="K45" s="137"/>
-      <c r="L45" s="137"/>
-      <c r="M45" s="137"/>
+      <c r="B45" s="175"/>
+      <c r="C45" s="175"/>
+      <c r="D45" s="175"/>
+      <c r="E45" s="175"/>
+      <c r="F45" s="175"/>
+      <c r="G45" s="175"/>
+      <c r="H45" s="175"/>
+      <c r="I45" s="175"/>
+      <c r="J45" s="175"/>
+      <c r="K45" s="175"/>
+      <c r="L45" s="175"/>
+      <c r="M45" s="175"/>
     </row>
     <row r="46" spans="2:14" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B46" s="137" t="s">
+      <c r="B46" s="175" t="s">
         <v>160</v>
       </c>
-      <c r="C46" s="137"/>
-      <c r="D46" s="137"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="137"/>
-      <c r="J46" s="137"/>
-      <c r="K46" s="137"/>
-      <c r="L46" s="137"/>
-      <c r="M46" s="137"/>
+      <c r="C46" s="175"/>
+      <c r="D46" s="175"/>
+      <c r="E46" s="175"/>
+      <c r="F46" s="175"/>
+      <c r="G46" s="175"/>
+      <c r="H46" s="175"/>
+      <c r="I46" s="175"/>
+      <c r="J46" s="175"/>
+      <c r="K46" s="175"/>
+      <c r="L46" s="175"/>
+      <c r="M46" s="175"/>
     </row>
     <row r="47" spans="2:14" ht="24.75" customHeight="1">
-      <c r="B47" s="138" t="s">
+      <c r="B47" s="176" t="s">
         <v>161</v>
       </c>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="138"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
       <c r="F47" s="51"/>
       <c r="G47" s="51"/>
       <c r="H47" s="51"/>
@@ -5226,12 +5625,12 @@
       <c r="M47" s="51"/>
     </row>
     <row r="48" spans="2:14" ht="24.75" customHeight="1">
-      <c r="B48" s="130" t="s">
+      <c r="B48" s="169" t="s">
         <v>162</v>
       </c>
-      <c r="C48" s="131"/>
-      <c r="D48" s="131"/>
-      <c r="E48" s="132"/>
+      <c r="C48" s="170"/>
+      <c r="D48" s="170"/>
+      <c r="E48" s="171"/>
       <c r="F48" s="51"/>
       <c r="G48" s="51"/>
       <c r="H48" s="51"/>
@@ -5242,12 +5641,12 @@
       <c r="M48" s="51"/>
     </row>
     <row r="49" spans="2:13" ht="24.75" customHeight="1">
-      <c r="B49" s="130" t="s">
+      <c r="B49" s="169" t="s">
         <v>163</v>
       </c>
-      <c r="C49" s="131"/>
-      <c r="D49" s="131"/>
-      <c r="E49" s="132"/>
+      <c r="C49" s="170"/>
+      <c r="D49" s="170"/>
+      <c r="E49" s="171"/>
       <c r="F49" s="51"/>
       <c r="G49" s="51"/>
       <c r="H49" s="51"/>
@@ -5272,59 +5671,47 @@
       <c r="M50" s="51"/>
     </row>
     <row r="51" spans="2:13" ht="24.75" customHeight="1">
-      <c r="B51" s="133" t="s">
+      <c r="B51" s="172" t="s">
         <v>164</v>
       </c>
-      <c r="C51" s="133"/>
-      <c r="D51" s="133"/>
-      <c r="E51" s="133"/>
-      <c r="F51" s="133"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="133"/>
-      <c r="I51" s="133"/>
+      <c r="C51" s="172"/>
+      <c r="D51" s="172"/>
+      <c r="E51" s="172"/>
+      <c r="F51" s="172"/>
+      <c r="G51" s="172"/>
+      <c r="H51" s="172"/>
+      <c r="I51" s="172"/>
       <c r="J51" s="54"/>
       <c r="K51" s="54"/>
       <c r="L51" s="55"/>
       <c r="M51" s="54"/>
     </row>
     <row r="52" spans="2:13" ht="24.75" customHeight="1">
-      <c r="B52" s="133"/>
-      <c r="C52" s="133"/>
-      <c r="D52" s="133"/>
-      <c r="E52" s="133"/>
-      <c r="F52" s="133"/>
-      <c r="G52" s="133"/>
-      <c r="H52" s="133"/>
-      <c r="I52" s="133"/>
+      <c r="B52" s="172"/>
+      <c r="C52" s="172"/>
+      <c r="D52" s="172"/>
+      <c r="E52" s="172"/>
+      <c r="F52" s="172"/>
+      <c r="G52" s="172"/>
+      <c r="H52" s="172"/>
+      <c r="I52" s="172"/>
       <c r="J52" s="54"/>
       <c r="K52" s="54"/>
       <c r="L52" s="55"/>
       <c r="M52" s="54"/>
     </row>
     <row r="53" spans="2:13" ht="24.75" customHeight="1">
-      <c r="B53" s="133"/>
-      <c r="C53" s="133"/>
-      <c r="D53" s="133"/>
-      <c r="E53" s="133"/>
-      <c r="F53" s="133"/>
-      <c r="G53" s="133"/>
-      <c r="H53" s="133"/>
-      <c r="I53" s="133"/>
+      <c r="B53" s="172"/>
+      <c r="C53" s="172"/>
+      <c r="D53" s="172"/>
+      <c r="E53" s="172"/>
+      <c r="F53" s="172"/>
+      <c r="G53" s="172"/>
+      <c r="H53" s="172"/>
+      <c r="I53" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E1:L2"/>
-    <mergeCell ref="E3:L4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="I5:M5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B49:E49"/>
     <mergeCell ref="B51:I53"/>
@@ -5334,6 +5721,18 @@
     <mergeCell ref="B45:M45"/>
     <mergeCell ref="B46:M46"/>
     <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:L2"/>
+    <mergeCell ref="E3:L4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="I5:M5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
@@ -5365,38 +5764,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="57" customFormat="1" ht="42.75" customHeight="1">
-      <c r="B1" s="167" t="s">
+      <c r="B1" s="177" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="177"/>
+      <c r="J1" s="177"/>
+      <c r="K1" s="177"/>
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
+      <c r="N1" s="177"/>
     </row>
     <row r="2" spans="1:16" s="57" customFormat="1" ht="42.75" customHeight="1">
       <c r="B2" s="58"/>
-      <c r="C2" s="168" t="s">
+      <c r="C2" s="178" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="178"/>
+      <c r="M2" s="178"/>
+      <c r="N2" s="178"/>
     </row>
     <row r="3" spans="1:16" s="57" customFormat="1" ht="15.75" customHeight="1">
       <c r="B3" s="59" t="s">
@@ -5414,32 +5813,32 @@
       <c r="L3" s="61"/>
     </row>
     <row r="4" spans="1:16" s="57" customFormat="1" ht="31.5" customHeight="1">
-      <c r="B4" s="169" t="s">
+      <c r="B4" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
+      <c r="L4" s="179"/>
+      <c r="M4" s="179"/>
+      <c r="N4" s="179"/>
     </row>
     <row r="5" spans="1:16" s="48" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="31"/>
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134" t="s">
+      <c r="C5" s="168"/>
+      <c r="D5" s="168" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="134"/>
+      <c r="E5" s="168"/>
       <c r="F5" s="33"/>
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
@@ -5453,14 +5852,14 @@
       <c r="P5" s="62"/>
     </row>
     <row r="6" spans="1:16" s="38" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="135" t="s">
+      <c r="C6" s="168"/>
+      <c r="D6" s="173" t="s">
         <v>169</v>
       </c>
-      <c r="E6" s="135"/>
+      <c r="E6" s="173"/>
       <c r="F6" s="40"/>
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
@@ -6633,189 +7032,189 @@
       <c r="P34" s="72"/>
     </row>
     <row r="35" spans="2:16" s="44" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B35" s="155" t="s">
+      <c r="B35" s="183" t="s">
         <v>237</v>
       </c>
-      <c r="C35" s="156"/>
-      <c r="D35" s="157"/>
-      <c r="E35" s="158"/>
-      <c r="F35" s="159"/>
-      <c r="G35" s="159"/>
-      <c r="H35" s="159"/>
-      <c r="I35" s="159"/>
-      <c r="J35" s="159"/>
-      <c r="K35" s="159"/>
-      <c r="L35" s="159"/>
-      <c r="M35" s="159"/>
-      <c r="N35" s="160"/>
-      <c r="O35" s="161"/>
-      <c r="P35" s="161"/>
+      <c r="C35" s="184"/>
+      <c r="D35" s="185"/>
+      <c r="E35" s="186"/>
+      <c r="F35" s="187"/>
+      <c r="G35" s="187"/>
+      <c r="H35" s="187"/>
+      <c r="I35" s="187"/>
+      <c r="J35" s="187"/>
+      <c r="K35" s="187"/>
+      <c r="L35" s="187"/>
+      <c r="M35" s="187"/>
+      <c r="N35" s="188"/>
+      <c r="O35" s="189"/>
+      <c r="P35" s="189"/>
     </row>
     <row r="36" spans="2:16" s="44" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B36" s="155" t="s">
+      <c r="B36" s="183" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="156"/>
-      <c r="D36" s="157"/>
-      <c r="E36" s="158" t="s">
+      <c r="C36" s="184"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="186" t="s">
         <v>239</v>
       </c>
-      <c r="F36" s="159"/>
-      <c r="G36" s="159"/>
-      <c r="H36" s="159"/>
-      <c r="I36" s="159"/>
-      <c r="J36" s="159"/>
-      <c r="K36" s="159"/>
-      <c r="L36" s="159"/>
-      <c r="M36" s="159"/>
-      <c r="N36" s="160"/>
-      <c r="O36" s="161">
+      <c r="F36" s="187"/>
+      <c r="G36" s="187"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="187"/>
+      <c r="K36" s="187"/>
+      <c r="L36" s="187"/>
+      <c r="M36" s="187"/>
+      <c r="N36" s="188"/>
+      <c r="O36" s="189">
         <f>P33</f>
         <v>43747.899999999994</v>
       </c>
-      <c r="P36" s="161"/>
+      <c r="P36" s="189"/>
     </row>
     <row r="37" spans="2:16" s="44" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B37" s="155" t="s">
+      <c r="B37" s="183" t="s">
         <v>240</v>
       </c>
-      <c r="C37" s="156"/>
-      <c r="D37" s="157"/>
-      <c r="E37" s="158"/>
-      <c r="F37" s="159"/>
-      <c r="G37" s="159"/>
-      <c r="H37" s="159"/>
-      <c r="I37" s="159"/>
-      <c r="J37" s="159"/>
-      <c r="K37" s="159"/>
-      <c r="L37" s="159"/>
-      <c r="M37" s="159"/>
-      <c r="N37" s="160"/>
-      <c r="O37" s="161">
+      <c r="C37" s="184"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="186"/>
+      <c r="F37" s="187"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="187"/>
+      <c r="I37" s="187"/>
+      <c r="J37" s="187"/>
+      <c r="K37" s="187"/>
+      <c r="L37" s="187"/>
+      <c r="M37" s="187"/>
+      <c r="N37" s="188"/>
+      <c r="O37" s="189">
         <f>SUM(O35:P36)</f>
         <v>43747.899999999994</v>
       </c>
-      <c r="P37" s="161"/>
+      <c r="P37" s="189"/>
     </row>
     <row r="38" spans="2:16" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B38" s="162"/>
-      <c r="C38" s="162"/>
-      <c r="D38" s="162"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="162"/>
-      <c r="G38" s="162"/>
-      <c r="H38" s="162"/>
-      <c r="I38" s="162"/>
-      <c r="J38" s="162"/>
-      <c r="K38" s="162"/>
-      <c r="L38" s="162"/>
-      <c r="M38" s="162"/>
-      <c r="N38" s="162"/>
+      <c r="B38" s="190"/>
+      <c r="C38" s="190"/>
+      <c r="D38" s="190"/>
+      <c r="E38" s="190"/>
+      <c r="F38" s="190"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="190"/>
+      <c r="K38" s="190"/>
+      <c r="L38" s="190"/>
+      <c r="M38" s="190"/>
+      <c r="N38" s="190"/>
       <c r="P38" s="74"/>
     </row>
     <row r="39" spans="2:16" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B39" s="137" t="s">
+      <c r="B39" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="163"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="137"/>
-      <c r="I39" s="137"/>
-      <c r="J39" s="137"/>
-      <c r="K39" s="137"/>
-      <c r="L39" s="137"/>
-      <c r="M39" s="137"/>
-      <c r="N39" s="137"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="175"/>
+      <c r="E39" s="175"/>
+      <c r="F39" s="175"/>
+      <c r="G39" s="175"/>
+      <c r="H39" s="175"/>
+      <c r="I39" s="175"/>
+      <c r="J39" s="175"/>
+      <c r="K39" s="175"/>
+      <c r="L39" s="175"/>
+      <c r="M39" s="175"/>
+      <c r="N39" s="175"/>
       <c r="P39" s="74"/>
     </row>
     <row r="40" spans="2:16" ht="24.75" customHeight="1">
-      <c r="B40" s="164" t="s">
+      <c r="B40" s="180" t="s">
         <v>242</v>
       </c>
-      <c r="C40" s="165"/>
-      <c r="D40" s="165"/>
-      <c r="E40" s="165"/>
-      <c r="F40" s="165"/>
-      <c r="G40" s="165"/>
-      <c r="H40" s="165"/>
-      <c r="I40" s="165"/>
-      <c r="J40" s="166"/>
+      <c r="C40" s="181"/>
+      <c r="D40" s="181"/>
+      <c r="E40" s="181"/>
+      <c r="F40" s="181"/>
+      <c r="G40" s="181"/>
+      <c r="H40" s="181"/>
+      <c r="I40" s="181"/>
+      <c r="J40" s="182"/>
     </row>
     <row r="41" spans="2:16" ht="24.75" customHeight="1">
-      <c r="B41" s="149" t="s">
+      <c r="B41" s="198" t="s">
         <v>243</v>
       </c>
-      <c r="C41" s="150"/>
-      <c r="D41" s="150"/>
-      <c r="E41" s="151"/>
-      <c r="F41" s="149" t="s">
+      <c r="C41" s="199"/>
+      <c r="D41" s="199"/>
+      <c r="E41" s="200"/>
+      <c r="F41" s="198" t="s">
         <v>244</v>
       </c>
-      <c r="G41" s="150"/>
-      <c r="H41" s="150"/>
-      <c r="I41" s="150"/>
-      <c r="J41" s="151"/>
+      <c r="G41" s="199"/>
+      <c r="H41" s="199"/>
+      <c r="I41" s="199"/>
+      <c r="J41" s="200"/>
     </row>
     <row r="42" spans="2:16" ht="24.75" customHeight="1">
-      <c r="B42" s="152" t="s">
+      <c r="B42" s="201" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="153"/>
-      <c r="D42" s="153"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="152" t="s">
+      <c r="C42" s="202"/>
+      <c r="D42" s="202"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="201" t="s">
         <v>246</v>
       </c>
-      <c r="G42" s="153"/>
-      <c r="H42" s="153"/>
-      <c r="I42" s="153"/>
-      <c r="J42" s="154"/>
+      <c r="G42" s="202"/>
+      <c r="H42" s="202"/>
+      <c r="I42" s="202"/>
+      <c r="J42" s="203"/>
     </row>
     <row r="43" spans="2:16" ht="24.75" customHeight="1">
-      <c r="B43" s="152" t="s">
+      <c r="B43" s="201" t="s">
         <v>247</v>
       </c>
-      <c r="C43" s="153"/>
-      <c r="D43" s="153"/>
-      <c r="E43" s="154"/>
-      <c r="F43" s="152" t="s">
+      <c r="C43" s="202"/>
+      <c r="D43" s="202"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="201" t="s">
         <v>248</v>
       </c>
-      <c r="G43" s="153"/>
-      <c r="H43" s="153"/>
-      <c r="I43" s="153"/>
-      <c r="J43" s="154"/>
+      <c r="G43" s="202"/>
+      <c r="H43" s="202"/>
+      <c r="I43" s="202"/>
+      <c r="J43" s="203"/>
     </row>
     <row r="44" spans="2:16" ht="24.75" customHeight="1">
-      <c r="B44" s="143" t="s">
+      <c r="B44" s="192" t="s">
         <v>249</v>
       </c>
-      <c r="C44" s="144"/>
-      <c r="D44" s="144"/>
-      <c r="E44" s="145"/>
-      <c r="F44" s="143" t="s">
+      <c r="C44" s="193"/>
+      <c r="D44" s="193"/>
+      <c r="E44" s="194"/>
+      <c r="F44" s="192" t="s">
         <v>250</v>
       </c>
-      <c r="G44" s="144"/>
-      <c r="H44" s="144"/>
-      <c r="I44" s="144"/>
-      <c r="J44" s="145"/>
+      <c r="G44" s="193"/>
+      <c r="H44" s="193"/>
+      <c r="I44" s="193"/>
+      <c r="J44" s="194"/>
     </row>
     <row r="45" spans="2:16" ht="24.75" customHeight="1">
-      <c r="B45" s="146" t="s">
+      <c r="B45" s="195" t="s">
         <v>251</v>
       </c>
-      <c r="C45" s="147"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="147"/>
-      <c r="F45" s="147"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="147"/>
-      <c r="I45" s="147"/>
-      <c r="J45" s="148"/>
+      <c r="C45" s="196"/>
+      <c r="D45" s="196"/>
+      <c r="E45" s="196"/>
+      <c r="F45" s="196"/>
+      <c r="G45" s="196"/>
+      <c r="H45" s="196"/>
+      <c r="I45" s="196"/>
+      <c r="J45" s="197"/>
     </row>
     <row r="46" spans="2:16" ht="24.75" customHeight="1">
       <c r="B46" s="75" t="s">
@@ -6839,13 +7238,15 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="F44:J44"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F42:J42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:J43"/>
     <mergeCell ref="B40:J40"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="E35:N35"/>
@@ -6858,15 +7259,13 @@
     <mergeCell ref="O37:P37"/>
     <mergeCell ref="B38:N38"/>
     <mergeCell ref="B39:N39"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="F44:J44"/>
-    <mergeCell ref="B45:J45"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="F41:J41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="F42:J42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="F43:J43"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
@@ -6904,46 +7303,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="89" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="206" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="179"/>
-      <c r="O1" s="179"/>
-      <c r="P1" s="179"/>
-      <c r="Q1" s="180"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="208"/>
     </row>
     <row r="2" spans="1:17" ht="25.5">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
-      <c r="L2" s="182"/>
-      <c r="M2" s="182"/>
-      <c r="N2" s="182"/>
-      <c r="O2" s="182"/>
-      <c r="P2" s="182"/>
-      <c r="Q2" s="183"/>
+      <c r="B2" s="210"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="210"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="210"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="210"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="210"/>
+      <c r="P2" s="210"/>
+      <c r="Q2" s="211"/>
     </row>
     <row r="3" spans="1:17" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -7931,39 +8330,39 @@
       <c r="Q24" s="17"/>
     </row>
     <row r="25" spans="1:17" ht="18" customHeight="1">
-      <c r="A25" s="184" t="s">
+      <c r="A25" s="212" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="185"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
-      <c r="N25" s="185"/>
-      <c r="O25" s="185"/>
-      <c r="P25" s="185"/>
-      <c r="Q25" s="186"/>
+      <c r="B25" s="213"/>
+      <c r="C25" s="213"/>
+      <c r="D25" s="213"/>
+      <c r="E25" s="213"/>
+      <c r="F25" s="213"/>
+      <c r="G25" s="213"/>
+      <c r="H25" s="213"/>
+      <c r="I25" s="213"/>
+      <c r="J25" s="213"/>
+      <c r="K25" s="213"/>
+      <c r="L25" s="213"/>
+      <c r="M25" s="213"/>
+      <c r="N25" s="213"/>
+      <c r="O25" s="213"/>
+      <c r="P25" s="213"/>
+      <c r="Q25" s="214"/>
     </row>
     <row r="26" spans="1:17" ht="15.5">
-      <c r="A26" s="187"/>
-      <c r="B26" s="188"/>
-      <c r="C26" s="188"/>
-      <c r="D26" s="188"/>
-      <c r="E26" s="188"/>
-      <c r="F26" s="188"/>
-      <c r="G26" s="188"/>
-      <c r="H26" s="188"/>
-      <c r="I26" s="188"/>
-      <c r="J26" s="188"/>
-      <c r="K26" s="188"/>
-      <c r="L26" s="188"/>
+      <c r="A26" s="215"/>
+      <c r="B26" s="216"/>
+      <c r="C26" s="216"/>
+      <c r="D26" s="216"/>
+      <c r="E26" s="216"/>
+      <c r="F26" s="216"/>
+      <c r="G26" s="216"/>
+      <c r="H26" s="216"/>
+      <c r="I26" s="216"/>
+      <c r="J26" s="216"/>
+      <c r="K26" s="216"/>
+      <c r="L26" s="216"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
@@ -7971,20 +8370,20 @@
       <c r="Q26" s="19"/>
     </row>
     <row r="27" spans="1:17" ht="18" customHeight="1">
-      <c r="A27" s="172" t="s">
+      <c r="A27" s="217" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="173"/>
-      <c r="C27" s="173"/>
-      <c r="D27" s="173"/>
-      <c r="E27" s="173"/>
-      <c r="F27" s="173"/>
-      <c r="G27" s="173"/>
-      <c r="H27" s="173"/>
-      <c r="I27" s="173"/>
-      <c r="J27" s="173"/>
-      <c r="K27" s="173"/>
-      <c r="L27" s="173"/>
+      <c r="B27" s="218"/>
+      <c r="C27" s="218"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="218"/>
+      <c r="F27" s="218"/>
+      <c r="G27" s="218"/>
+      <c r="H27" s="218"/>
+      <c r="I27" s="218"/>
+      <c r="J27" s="218"/>
+      <c r="K27" s="218"/>
+      <c r="L27" s="218"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
@@ -7992,20 +8391,20 @@
       <c r="Q27" s="20"/>
     </row>
     <row r="28" spans="1:17" ht="18" customHeight="1">
-      <c r="A28" s="174" t="s">
+      <c r="A28" s="204" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="175"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="175"/>
-      <c r="E28" s="175"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="175"/>
-      <c r="I28" s="175"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="175"/>
-      <c r="L28" s="175"/>
+      <c r="B28" s="205"/>
+      <c r="C28" s="205"/>
+      <c r="D28" s="205"/>
+      <c r="E28" s="205"/>
+      <c r="F28" s="205"/>
+      <c r="G28" s="205"/>
+      <c r="H28" s="205"/>
+      <c r="I28" s="205"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="205"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="18"/>
@@ -8013,20 +8412,20 @@
       <c r="Q28" s="21"/>
     </row>
     <row r="29" spans="1:17" ht="18" customHeight="1">
-      <c r="A29" s="172" t="s">
+      <c r="A29" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="173"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="173"/>
-      <c r="H29" s="173"/>
-      <c r="I29" s="173"/>
-      <c r="J29" s="173"/>
-      <c r="K29" s="173"/>
-      <c r="L29" s="173"/>
+      <c r="B29" s="218"/>
+      <c r="C29" s="218"/>
+      <c r="D29" s="218"/>
+      <c r="E29" s="218"/>
+      <c r="F29" s="218"/>
+      <c r="G29" s="218"/>
+      <c r="H29" s="218"/>
+      <c r="I29" s="218"/>
+      <c r="J29" s="218"/>
+      <c r="K29" s="218"/>
+      <c r="L29" s="218"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
@@ -8034,20 +8433,20 @@
       <c r="Q29" s="20"/>
     </row>
     <row r="30" spans="1:17" ht="18" customHeight="1">
-      <c r="A30" s="174" t="s">
+      <c r="A30" s="204" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="175"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="175"/>
-      <c r="E30" s="175"/>
-      <c r="F30" s="175"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="175"/>
-      <c r="I30" s="175"/>
-      <c r="J30" s="175"/>
-      <c r="K30" s="175"/>
-      <c r="L30" s="175"/>
+      <c r="B30" s="205"/>
+      <c r="C30" s="205"/>
+      <c r="D30" s="205"/>
+      <c r="E30" s="205"/>
+      <c r="F30" s="205"/>
+      <c r="G30" s="205"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="205"/>
+      <c r="L30" s="205"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="18"/>
@@ -8055,20 +8454,20 @@
       <c r="Q30" s="21"/>
     </row>
     <row r="31" spans="1:17" ht="18" customHeight="1">
-      <c r="A31" s="174" t="s">
+      <c r="A31" s="204" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="175"/>
-      <c r="C31" s="175"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="175"/>
-      <c r="F31" s="175"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="175"/>
-      <c r="I31" s="175"/>
-      <c r="J31" s="175"/>
-      <c r="K31" s="175"/>
-      <c r="L31" s="175"/>
+      <c r="B31" s="205"/>
+      <c r="C31" s="205"/>
+      <c r="D31" s="205"/>
+      <c r="E31" s="205"/>
+      <c r="F31" s="205"/>
+      <c r="G31" s="205"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="205"/>
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="18"/>
@@ -8076,20 +8475,20 @@
       <c r="Q31" s="21"/>
     </row>
     <row r="32" spans="1:17" ht="18" customHeight="1">
-      <c r="A32" s="174" t="s">
+      <c r="A32" s="204" t="s">
         <v>291</v>
       </c>
-      <c r="B32" s="175"/>
-      <c r="C32" s="175"/>
-      <c r="D32" s="175"/>
-      <c r="E32" s="175"/>
-      <c r="F32" s="175"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="175"/>
-      <c r="I32" s="175"/>
-      <c r="J32" s="175"/>
-      <c r="K32" s="175"/>
-      <c r="L32" s="175"/>
+      <c r="B32" s="205"/>
+      <c r="C32" s="205"/>
+      <c r="D32" s="205"/>
+      <c r="E32" s="205"/>
+      <c r="F32" s="205"/>
+      <c r="G32" s="205"/>
+      <c r="H32" s="205"/>
+      <c r="I32" s="205"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="205"/>
+      <c r="L32" s="205"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
@@ -8097,20 +8496,20 @@
       <c r="Q32" s="21"/>
     </row>
     <row r="33" spans="1:17" ht="18" customHeight="1">
-      <c r="A33" s="174" t="s">
+      <c r="A33" s="204" t="s">
         <v>292</v>
       </c>
-      <c r="B33" s="175"/>
-      <c r="C33" s="175"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="175"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="175"/>
-      <c r="I33" s="175"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="175"/>
-      <c r="L33" s="175"/>
+      <c r="B33" s="205"/>
+      <c r="C33" s="205"/>
+      <c r="D33" s="205"/>
+      <c r="E33" s="205"/>
+      <c r="F33" s="205"/>
+      <c r="G33" s="205"/>
+      <c r="H33" s="205"/>
+      <c r="I33" s="205"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="205"/>
+      <c r="L33" s="205"/>
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
       <c r="O33" s="18"/>
@@ -8118,20 +8517,20 @@
       <c r="Q33" s="21"/>
     </row>
     <row r="34" spans="1:17" ht="18" customHeight="1" thickBot="1">
-      <c r="A34" s="176" t="s">
+      <c r="A34" s="221" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="177"/>
-      <c r="C34" s="177"/>
-      <c r="D34" s="177"/>
-      <c r="E34" s="177"/>
-      <c r="F34" s="177"/>
-      <c r="G34" s="177"/>
-      <c r="H34" s="177"/>
-      <c r="I34" s="177"/>
-      <c r="J34" s="177"/>
-      <c r="K34" s="177"/>
-      <c r="L34" s="177"/>
+      <c r="B34" s="222"/>
+      <c r="C34" s="222"/>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="222"/>
+      <c r="G34" s="222"/>
+      <c r="H34" s="222"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="222"/>
+      <c r="K34" s="222"/>
+      <c r="L34" s="222"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="18"/>
@@ -8139,20 +8538,20 @@
       <c r="Q34" s="21"/>
     </row>
     <row r="35" spans="1:17" ht="16" customHeight="1" thickBot="1">
-      <c r="A35" s="170" t="s">
+      <c r="A35" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="171"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="171"/>
-      <c r="I35" s="171"/>
-      <c r="J35" s="171"/>
-      <c r="K35" s="171"/>
-      <c r="L35" s="171"/>
+      <c r="B35" s="220"/>
+      <c r="C35" s="220"/>
+      <c r="D35" s="220"/>
+      <c r="E35" s="220"/>
+      <c r="F35" s="220"/>
+      <c r="G35" s="220"/>
+      <c r="H35" s="220"/>
+      <c r="I35" s="220"/>
+      <c r="J35" s="220"/>
+      <c r="K35" s="220"/>
+      <c r="L35" s="220"/>
       <c r="M35" s="23"/>
       <c r="N35" s="23"/>
       <c r="O35" s="23"/>
@@ -8162,12 +8561,6 @@
   </sheetData>
   <autoFilter ref="A7:Q35" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="13">
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A25:Q25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A35:L35"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="A30:L30"/>
@@ -8175,6 +8568,12 @@
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8212,46 +8611,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="89" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="206" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="179"/>
-      <c r="O1" s="179"/>
-      <c r="P1" s="179"/>
-      <c r="Q1" s="180"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="207"/>
+      <c r="M1" s="207"/>
+      <c r="N1" s="207"/>
+      <c r="O1" s="207"/>
+      <c r="P1" s="207"/>
+      <c r="Q1" s="208"/>
     </row>
     <row r="2" spans="1:17" ht="25.5">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
-      <c r="I2" s="182"/>
-      <c r="J2" s="182"/>
-      <c r="K2" s="182"/>
-      <c r="L2" s="182"/>
-      <c r="M2" s="182"/>
-      <c r="N2" s="182"/>
-      <c r="O2" s="182"/>
-      <c r="P2" s="182"/>
-      <c r="Q2" s="183"/>
+      <c r="B2" s="210"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="210"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="210"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="210"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="210"/>
+      <c r="P2" s="210"/>
+      <c r="Q2" s="211"/>
     </row>
     <row r="3" spans="1:17" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8840,39 +9239,39 @@
       <c r="Q17" s="78"/>
     </row>
     <row r="18" spans="1:17" ht="18" customHeight="1">
-      <c r="A18" s="184" t="s">
+      <c r="A18" s="212" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="185"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185"/>
-      <c r="F18" s="185"/>
-      <c r="G18" s="185"/>
-      <c r="H18" s="185"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="185"/>
-      <c r="K18" s="185"/>
-      <c r="L18" s="185"/>
-      <c r="M18" s="185"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="185"/>
-      <c r="P18" s="185"/>
-      <c r="Q18" s="186"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="213"/>
+      <c r="D18" s="213"/>
+      <c r="E18" s="213"/>
+      <c r="F18" s="213"/>
+      <c r="G18" s="213"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="213"/>
+      <c r="J18" s="213"/>
+      <c r="K18" s="213"/>
+      <c r="L18" s="213"/>
+      <c r="M18" s="213"/>
+      <c r="N18" s="213"/>
+      <c r="O18" s="213"/>
+      <c r="P18" s="213"/>
+      <c r="Q18" s="214"/>
     </row>
     <row r="19" spans="1:17" ht="15.5">
-      <c r="A19" s="187"/>
-      <c r="B19" s="188"/>
-      <c r="C19" s="188"/>
-      <c r="D19" s="188"/>
-      <c r="E19" s="188"/>
-      <c r="F19" s="188"/>
-      <c r="G19" s="188"/>
-      <c r="H19" s="188"/>
-      <c r="I19" s="188"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="188"/>
-      <c r="L19" s="188"/>
+      <c r="A19" s="215"/>
+      <c r="B19" s="216"/>
+      <c r="C19" s="216"/>
+      <c r="D19" s="216"/>
+      <c r="E19" s="216"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="216"/>
+      <c r="H19" s="216"/>
+      <c r="I19" s="216"/>
+      <c r="J19" s="216"/>
+      <c r="K19" s="216"/>
+      <c r="L19" s="216"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="18"/>
@@ -8880,20 +9279,20 @@
       <c r="Q19" s="19"/>
     </row>
     <row r="20" spans="1:17" ht="18" customHeight="1">
-      <c r="A20" s="172" t="s">
+      <c r="A20" s="217" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="173"/>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="173"/>
-      <c r="H20" s="173"/>
-      <c r="I20" s="173"/>
-      <c r="J20" s="173"/>
-      <c r="K20" s="173"/>
-      <c r="L20" s="173"/>
+      <c r="B20" s="218"/>
+      <c r="C20" s="218"/>
+      <c r="D20" s="218"/>
+      <c r="E20" s="218"/>
+      <c r="F20" s="218"/>
+      <c r="G20" s="218"/>
+      <c r="H20" s="218"/>
+      <c r="I20" s="218"/>
+      <c r="J20" s="218"/>
+      <c r="K20" s="218"/>
+      <c r="L20" s="218"/>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
@@ -8901,20 +9300,20 @@
       <c r="Q20" s="20"/>
     </row>
     <row r="21" spans="1:17" ht="18" customHeight="1">
-      <c r="A21" s="174" t="s">
+      <c r="A21" s="204" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="175"/>
-      <c r="C21" s="175"/>
-      <c r="D21" s="175"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="175"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="175"/>
-      <c r="I21" s="175"/>
-      <c r="J21" s="175"/>
-      <c r="K21" s="175"/>
-      <c r="L21" s="175"/>
+      <c r="B21" s="205"/>
+      <c r="C21" s="205"/>
+      <c r="D21" s="205"/>
+      <c r="E21" s="205"/>
+      <c r="F21" s="205"/>
+      <c r="G21" s="205"/>
+      <c r="H21" s="205"/>
+      <c r="I21" s="205"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="205"/>
+      <c r="L21" s="205"/>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
@@ -8922,20 +9321,20 @@
       <c r="Q21" s="21"/>
     </row>
     <row r="22" spans="1:17" ht="18" customHeight="1">
-      <c r="A22" s="172" t="s">
+      <c r="A22" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="173"/>
-      <c r="C22" s="173"/>
-      <c r="D22" s="173"/>
-      <c r="E22" s="173"/>
-      <c r="F22" s="173"/>
-      <c r="G22" s="173"/>
-      <c r="H22" s="173"/>
-      <c r="I22" s="173"/>
-      <c r="J22" s="173"/>
-      <c r="K22" s="173"/>
-      <c r="L22" s="173"/>
+      <c r="B22" s="218"/>
+      <c r="C22" s="218"/>
+      <c r="D22" s="218"/>
+      <c r="E22" s="218"/>
+      <c r="F22" s="218"/>
+      <c r="G22" s="218"/>
+      <c r="H22" s="218"/>
+      <c r="I22" s="218"/>
+      <c r="J22" s="218"/>
+      <c r="K22" s="218"/>
+      <c r="L22" s="218"/>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
@@ -8943,20 +9342,20 @@
       <c r="Q22" s="20"/>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1">
-      <c r="A23" s="174" t="s">
+      <c r="A23" s="204" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="175"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="175"/>
-      <c r="E23" s="175"/>
-      <c r="F23" s="175"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="175"/>
-      <c r="I23" s="175"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="175"/>
-      <c r="L23" s="175"/>
+      <c r="B23" s="205"/>
+      <c r="C23" s="205"/>
+      <c r="D23" s="205"/>
+      <c r="E23" s="205"/>
+      <c r="F23" s="205"/>
+      <c r="G23" s="205"/>
+      <c r="H23" s="205"/>
+      <c r="I23" s="205"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="205"/>
+      <c r="L23" s="205"/>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
@@ -8964,20 +9363,20 @@
       <c r="Q23" s="21"/>
     </row>
     <row r="24" spans="1:17" ht="18" customHeight="1">
-      <c r="A24" s="174" t="s">
+      <c r="A24" s="204" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="175"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="175"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="175"/>
-      <c r="I24" s="175"/>
-      <c r="J24" s="175"/>
-      <c r="K24" s="175"/>
-      <c r="L24" s="175"/>
+      <c r="B24" s="205"/>
+      <c r="C24" s="205"/>
+      <c r="D24" s="205"/>
+      <c r="E24" s="205"/>
+      <c r="F24" s="205"/>
+      <c r="G24" s="205"/>
+      <c r="H24" s="205"/>
+      <c r="I24" s="205"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="205"/>
+      <c r="L24" s="205"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
@@ -8985,20 +9384,20 @@
       <c r="Q24" s="21"/>
     </row>
     <row r="25" spans="1:17" ht="18" customHeight="1">
-      <c r="A25" s="174" t="s">
+      <c r="A25" s="204" t="s">
         <v>291</v>
       </c>
-      <c r="B25" s="175"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="175"/>
-      <c r="I25" s="175"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="175"/>
-      <c r="L25" s="175"/>
+      <c r="B25" s="205"/>
+      <c r="C25" s="205"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="205"/>
+      <c r="F25" s="205"/>
+      <c r="G25" s="205"/>
+      <c r="H25" s="205"/>
+      <c r="I25" s="205"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="205"/>
+      <c r="L25" s="205"/>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
       <c r="O25" s="18"/>
@@ -9006,20 +9405,20 @@
       <c r="Q25" s="21"/>
     </row>
     <row r="26" spans="1:17" ht="18" customHeight="1">
-      <c r="A26" s="174" t="s">
+      <c r="A26" s="204" t="s">
         <v>292</v>
       </c>
-      <c r="B26" s="175"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="175"/>
-      <c r="E26" s="175"/>
-      <c r="F26" s="175"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="175"/>
-      <c r="I26" s="175"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="175"/>
-      <c r="L26" s="175"/>
+      <c r="B26" s="205"/>
+      <c r="C26" s="205"/>
+      <c r="D26" s="205"/>
+      <c r="E26" s="205"/>
+      <c r="F26" s="205"/>
+      <c r="G26" s="205"/>
+      <c r="H26" s="205"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="205"/>
+      <c r="L26" s="205"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
@@ -9027,20 +9426,20 @@
       <c r="Q26" s="21"/>
     </row>
     <row r="27" spans="1:17" ht="18" customHeight="1" thickBot="1">
-      <c r="A27" s="176" t="s">
+      <c r="A27" s="221" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="177"/>
-      <c r="C27" s="177"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="177"/>
-      <c r="F27" s="177"/>
-      <c r="G27" s="177"/>
-      <c r="H27" s="177"/>
-      <c r="I27" s="177"/>
-      <c r="J27" s="177"/>
-      <c r="K27" s="177"/>
-      <c r="L27" s="177"/>
+      <c r="B27" s="222"/>
+      <c r="C27" s="222"/>
+      <c r="D27" s="222"/>
+      <c r="E27" s="222"/>
+      <c r="F27" s="222"/>
+      <c r="G27" s="222"/>
+      <c r="H27" s="222"/>
+      <c r="I27" s="222"/>
+      <c r="J27" s="222"/>
+      <c r="K27" s="222"/>
+      <c r="L27" s="222"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
@@ -9048,20 +9447,20 @@
       <c r="Q27" s="21"/>
     </row>
     <row r="28" spans="1:17" ht="16" customHeight="1" thickBot="1">
-      <c r="A28" s="170" t="s">
+      <c r="A28" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="171"/>
-      <c r="C28" s="171"/>
-      <c r="D28" s="171"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="171"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="171"/>
+      <c r="B28" s="220"/>
+      <c r="C28" s="220"/>
+      <c r="D28" s="220"/>
+      <c r="E28" s="220"/>
+      <c r="F28" s="220"/>
+      <c r="G28" s="220"/>
+      <c r="H28" s="220"/>
+      <c r="I28" s="220"/>
+      <c r="J28" s="220"/>
+      <c r="K28" s="220"/>
+      <c r="L28" s="220"/>
       <c r="M28" s="23"/>
       <c r="N28" s="23"/>
       <c r="O28" s="23"/>
@@ -9071,12 +9470,6 @@
   </sheetData>
   <autoFilter ref="A7:Q28" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="13">
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="A18:Q18"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A20:L20"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
@@ -9084,6 +9477,12 @@
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A18:Q18"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A20:L20"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9118,54 +9517,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="44" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="158" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="200"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="158"/>
+      <c r="S1" s="158"/>
+      <c r="T1" s="225"/>
+      <c r="U1" s="158"/>
     </row>
     <row r="2" spans="1:22" ht="37" customHeight="1">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="158" t="s">
         <v>294</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="200"/>
-      <c r="N2" s="200"/>
-      <c r="O2" s="200"/>
-      <c r="P2" s="201"/>
-      <c r="Q2" s="201"/>
-      <c r="R2" s="200"/>
-      <c r="S2" s="200"/>
-      <c r="T2" s="201"/>
-      <c r="U2" s="200"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="225"/>
+      <c r="Q2" s="225"/>
+      <c r="R2" s="158"/>
+      <c r="S2" s="158"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="158"/>
     </row>
     <row r="3" spans="1:22" ht="29" customHeight="1">
       <c r="A3" s="79" t="s">
@@ -10292,19 +10691,19 @@
       <c r="U21" s="109"/>
     </row>
     <row r="22" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A22" s="202" t="s">
+      <c r="A22" s="159" t="s">
         <v>391</v>
       </c>
-      <c r="B22" s="202"/>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203"/>
-      <c r="G22" s="203"/>
-      <c r="H22" s="203"/>
-      <c r="I22" s="203"/>
-      <c r="J22" s="204"/>
-      <c r="K22" s="204"/>
+      <c r="B22" s="159"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="160"/>
+      <c r="I22" s="160"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="161"/>
       <c r="L22" s="106"/>
       <c r="M22" s="106"/>
       <c r="N22" s="106"/>
@@ -10415,23 +10814,23 @@
       <c r="U26" s="109"/>
     </row>
     <row r="27" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A27" s="189" t="s">
+      <c r="A27" s="149" t="s">
         <v>395</v>
       </c>
-      <c r="B27" s="189"/>
-      <c r="C27" s="189"/>
-      <c r="D27" s="189"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="189"/>
-      <c r="I27" s="189"/>
-      <c r="J27" s="189"/>
-      <c r="K27" s="189"/>
-      <c r="L27" s="189"/>
-      <c r="M27" s="189"/>
-      <c r="N27" s="189"/>
-      <c r="O27" s="189"/>
+      <c r="B27" s="149"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="150"/>
+      <c r="G27" s="149"/>
+      <c r="H27" s="149"/>
+      <c r="I27" s="149"/>
+      <c r="J27" s="149"/>
+      <c r="K27" s="149"/>
+      <c r="L27" s="149"/>
+      <c r="M27" s="149"/>
+      <c r="N27" s="149"/>
+      <c r="O27" s="149"/>
       <c r="P27" s="119"/>
       <c r="Q27" s="119"/>
       <c r="R27" s="117"/>
@@ -10440,23 +10839,23 @@
       <c r="U27" s="109"/>
     </row>
     <row r="28" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A28" s="189" t="s">
+      <c r="A28" s="149" t="s">
         <v>396</v>
       </c>
-      <c r="B28" s="189"/>
-      <c r="C28" s="189"/>
-      <c r="D28" s="189"/>
-      <c r="E28" s="189"/>
-      <c r="F28" s="190"/>
-      <c r="G28" s="189"/>
-      <c r="H28" s="189"/>
-      <c r="I28" s="189"/>
-      <c r="J28" s="189"/>
-      <c r="K28" s="189"/>
-      <c r="L28" s="189"/>
-      <c r="M28" s="189"/>
-      <c r="N28" s="189"/>
-      <c r="O28" s="189"/>
+      <c r="B28" s="149"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="149"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="150"/>
+      <c r="G28" s="149"/>
+      <c r="H28" s="149"/>
+      <c r="I28" s="149"/>
+      <c r="J28" s="149"/>
+      <c r="K28" s="149"/>
+      <c r="L28" s="149"/>
+      <c r="M28" s="149"/>
+      <c r="N28" s="149"/>
+      <c r="O28" s="149"/>
       <c r="P28" s="119"/>
       <c r="Q28" s="119"/>
       <c r="R28" s="117"/>
@@ -10488,65 +10887,65 @@
       <c r="U29" s="106"/>
     </row>
     <row r="30" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A30" s="205" t="s">
+      <c r="A30" s="162" t="s">
         <v>397</v>
       </c>
-      <c r="B30" s="205"/>
-      <c r="C30" s="205"/>
-      <c r="D30" s="205"/>
-      <c r="E30" s="205"/>
-      <c r="F30" s="206"/>
-      <c r="G30" s="205"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="205"/>
-      <c r="L30" s="206"/>
-      <c r="M30" s="206"/>
-      <c r="N30" s="206"/>
-      <c r="O30" s="206"/>
-      <c r="P30" s="207"/>
-      <c r="Q30" s="207"/>
-      <c r="R30" s="206"/>
-      <c r="S30" s="206"/>
-      <c r="T30" s="207"/>
-      <c r="U30" s="206"/>
+      <c r="B30" s="162"/>
+      <c r="C30" s="162"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="163"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="162"/>
+      <c r="K30" s="162"/>
+      <c r="L30" s="163"/>
+      <c r="M30" s="163"/>
+      <c r="N30" s="163"/>
+      <c r="O30" s="163"/>
+      <c r="P30" s="226"/>
+      <c r="Q30" s="226"/>
+      <c r="R30" s="163"/>
+      <c r="S30" s="163"/>
+      <c r="T30" s="226"/>
+      <c r="U30" s="163"/>
     </row>
     <row r="31" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A31" s="189" t="s">
+      <c r="A31" s="149" t="s">
         <v>398</v>
       </c>
-      <c r="B31" s="189"/>
-      <c r="C31" s="189"/>
-      <c r="D31" s="189"/>
-      <c r="E31" s="189"/>
-      <c r="F31" s="190"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="189"/>
-      <c r="I31" s="189"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="189"/>
-      <c r="L31" s="190"/>
-      <c r="M31" s="190"/>
-      <c r="N31" s="190"/>
-      <c r="O31" s="190"/>
-      <c r="P31" s="191"/>
-      <c r="Q31" s="191"/>
-      <c r="R31" s="190"/>
-      <c r="S31" s="190"/>
-      <c r="T31" s="191"/>
-      <c r="U31" s="190"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="149"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="149"/>
+      <c r="I31" s="149"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="223"/>
+      <c r="Q31" s="223"/>
+      <c r="R31" s="150"/>
+      <c r="S31" s="150"/>
+      <c r="T31" s="223"/>
+      <c r="U31" s="150"/>
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1">
-      <c r="A32" s="192"/>
-      <c r="B32" s="192"/>
-      <c r="C32" s="193"/>
-      <c r="D32" s="193"/>
-      <c r="E32" s="193"/>
-      <c r="F32" s="193"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="193"/>
-      <c r="I32" s="194"/>
+      <c r="A32" s="151"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
+      <c r="F32" s="152"/>
+      <c r="G32" s="152"/>
+      <c r="H32" s="152"/>
+      <c r="I32" s="153"/>
       <c r="J32" s="121"/>
       <c r="K32" s="122"/>
       <c r="L32" s="123"/>
@@ -10562,15 +10961,15 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A33" s="195"/>
-      <c r="B33" s="195"/>
-      <c r="C33" s="196"/>
-      <c r="D33" s="196"/>
-      <c r="E33" s="196"/>
-      <c r="F33" s="196"/>
-      <c r="G33" s="196"/>
-      <c r="H33" s="196"/>
-      <c r="I33" s="197"/>
+      <c r="A33" s="154"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="156"/>
       <c r="J33" s="118"/>
       <c r="K33" s="115"/>
       <c r="L33" s="126"/>
@@ -10585,21 +10984,21 @@
       <c r="U33" s="109"/>
     </row>
     <row r="34" spans="1:21" ht="14.4" customHeight="1">
-      <c r="A34" s="198"/>
-      <c r="B34" s="198"/>
-      <c r="C34" s="198"/>
-      <c r="D34" s="198"/>
-      <c r="E34" s="198"/>
-      <c r="F34" s="199"/>
-      <c r="G34" s="198"/>
-      <c r="H34" s="198"/>
-      <c r="I34" s="198"/>
-      <c r="J34" s="198"/>
-      <c r="K34" s="198"/>
-      <c r="L34" s="198"/>
-      <c r="M34" s="198"/>
-      <c r="N34" s="198"/>
-      <c r="O34" s="198"/>
+      <c r="A34" s="157"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="157"/>
+      <c r="E34" s="157"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="157"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="157"/>
+      <c r="L34" s="157"/>
+      <c r="M34" s="157"/>
+      <c r="N34" s="157"/>
+      <c r="O34" s="157"/>
       <c r="P34" s="129"/>
       <c r="Q34" s="129"/>
       <c r="R34" s="128"/>
@@ -10629,11 +11028,11 @@
   <dimension ref="B1:R43"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="24.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="215" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" style="134" customWidth="1"/>
     <col min="2" max="2" width="4.9140625" style="48" customWidth="1"/>
     <col min="3" max="3" width="10" style="48" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" style="48" customWidth="1"/>
-    <col min="5" max="7" width="18.9140625" style="224" customWidth="1"/>
+    <col min="5" max="7" width="18.9140625" style="140" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" style="48" customWidth="1"/>
     <col min="9" max="9" width="15" style="48" customWidth="1"/>
     <col min="10" max="11" width="9.6640625" style="48" customWidth="1"/>
@@ -10642,121 +11041,121 @@
     <col min="16" max="16" width="12.4140625" style="48" customWidth="1"/>
     <col min="17" max="17" width="8.83203125" style="48"/>
     <col min="18" max="18" width="22.83203125" style="48" customWidth="1"/>
-    <col min="19" max="16384" width="8.83203125" style="215"/>
+    <col min="19" max="16384" width="8.83203125" style="134"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" s="30" customFormat="1" ht="37" customHeight="1">
-      <c r="B1" s="208"/>
+      <c r="B1" s="130"/>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="209"/>
-      <c r="G1" s="209"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="29"/>
-      <c r="I1" s="210" t="s">
+      <c r="I1" s="230" t="s">
         <v>400</v>
       </c>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="210"/>
-      <c r="O1" s="210"/>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
+      <c r="O1" s="230"/>
+      <c r="P1" s="230"/>
+      <c r="Q1" s="230"/>
+      <c r="R1" s="230"/>
     </row>
     <row r="2" spans="2:18" s="30" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B2" s="208"/>
+      <c r="B2" s="130"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="209"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
       <c r="H2" s="29"/>
-      <c r="I2" s="211" t="s">
+      <c r="I2" s="231" t="s">
         <v>401</v>
       </c>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="M2" s="211"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="211"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="231"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="231"/>
+      <c r="P2" s="231"/>
+      <c r="Q2" s="231"/>
+      <c r="R2" s="231"/>
     </row>
     <row r="3" spans="2:18" s="30" customFormat="1" ht="35" customHeight="1">
-      <c r="B3" s="208"/>
+      <c r="B3" s="130"/>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="209"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="29"/>
-      <c r="I3" s="212" t="s">
+      <c r="I3" s="232" t="s">
         <v>402</v>
       </c>
-      <c r="J3" s="212"/>
-      <c r="K3" s="212"/>
-      <c r="L3" s="212"/>
-      <c r="M3" s="212"/>
-      <c r="N3" s="212"/>
-      <c r="O3" s="212"/>
-      <c r="P3" s="212"/>
-      <c r="Q3" s="212"/>
-      <c r="R3" s="212"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
+      <c r="M3" s="232"/>
+      <c r="N3" s="232"/>
+      <c r="O3" s="232"/>
+      <c r="P3" s="232"/>
+      <c r="Q3" s="232"/>
+      <c r="R3" s="232"/>
     </row>
     <row r="4" spans="2:18" s="30" customFormat="1" ht="26" customHeight="1">
-      <c r="B4" s="208"/>
+      <c r="B4" s="130"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
-      <c r="E4" s="209"/>
-      <c r="F4" s="209"/>
-      <c r="G4" s="209"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
       <c r="H4" s="29"/>
-      <c r="I4" s="212" t="s">
+      <c r="I4" s="232" t="s">
         <v>403</v>
       </c>
-      <c r="J4" s="212"/>
-      <c r="K4" s="212"/>
-      <c r="L4" s="212"/>
-      <c r="M4" s="212"/>
-      <c r="N4" s="212"/>
-      <c r="O4" s="212"/>
-      <c r="P4" s="212"/>
-      <c r="Q4" s="212"/>
-      <c r="R4" s="212"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
+      <c r="M4" s="232"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
     </row>
     <row r="5" spans="2:18" s="30" customFormat="1" ht="10" customHeight="1">
-      <c r="B5" s="213"/>
+      <c r="B5" s="132"/>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
       <c r="H5" s="29"/>
       <c r="I5" s="29"/>
-      <c r="J5" s="142"/>
-      <c r="K5" s="142"/>
-      <c r="L5" s="142"/>
-      <c r="M5" s="142"/>
-      <c r="N5" s="142"/>
-      <c r="O5" s="142"/>
-      <c r="P5" s="142"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="167"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="167"/>
+      <c r="O5" s="167"/>
+      <c r="P5" s="167"/>
       <c r="Q5" s="48"/>
       <c r="R5" s="48"/>
     </row>
     <row r="6" spans="2:18" s="30" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="168" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134" t="s">
+      <c r="C6" s="168"/>
+      <c r="D6" s="168" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="168"/>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
       <c r="H6" s="33"/>
@@ -10772,14 +11171,14 @@
       <c r="R6" s="48"/>
     </row>
     <row r="7" spans="2:18" s="30" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B7" s="134" t="s">
+      <c r="B7" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134" t="s">
+      <c r="C7" s="168"/>
+      <c r="D7" s="168" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="134"/>
+      <c r="E7" s="168"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32"/>
       <c r="H7" s="33"/>
@@ -10795,14 +11194,14 @@
       <c r="R7" s="48"/>
     </row>
     <row r="8" spans="2:18" s="30" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="134"/>
-      <c r="D8" s="134" t="s">
+      <c r="C8" s="168"/>
+      <c r="D8" s="168" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="134"/>
+      <c r="E8" s="168"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32"/>
       <c r="H8" s="36"/>
@@ -10818,14 +11217,14 @@
       <c r="R8" s="48"/>
     </row>
     <row r="9" spans="2:18" s="38" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="135" t="s">
+      <c r="C9" s="168"/>
+      <c r="D9" s="173" t="s">
         <v>405</v>
       </c>
-      <c r="E9" s="135"/>
+      <c r="E9" s="173"/>
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="40"/>
@@ -10901,13 +11300,13 @@
       <c r="D11" s="45" t="s">
         <v>409</v>
       </c>
-      <c r="E11" s="214" t="s">
+      <c r="E11" s="133" t="s">
         <v>410</v>
       </c>
-      <c r="F11" s="214" t="s">
+      <c r="F11" s="133" t="s">
         <v>411</v>
       </c>
-      <c r="G11" s="214"/>
+      <c r="G11" s="133"/>
       <c r="H11" s="47" t="s">
         <v>412</v>
       </c>
@@ -10948,13 +11347,13 @@
       <c r="D12" s="45" t="s">
         <v>409</v>
       </c>
-      <c r="E12" s="214" t="s">
+      <c r="E12" s="133" t="s">
         <v>410</v>
       </c>
-      <c r="F12" s="214" t="s">
+      <c r="F12" s="133" t="s">
         <v>411</v>
       </c>
-      <c r="G12" s="214"/>
+      <c r="G12" s="133"/>
       <c r="H12" s="47" t="s">
         <v>412</v>
       </c>
@@ -10995,13 +11394,13 @@
       <c r="D13" s="45" t="s">
         <v>419</v>
       </c>
-      <c r="E13" s="214" t="s">
+      <c r="E13" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="F13" s="214" t="s">
+      <c r="F13" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="G13" s="214" t="s">
+      <c r="G13" s="133" t="s">
         <v>420</v>
       </c>
       <c r="H13" s="47"/>
@@ -11044,13 +11443,13 @@
       <c r="D14" s="45" t="s">
         <v>419</v>
       </c>
-      <c r="E14" s="214" t="s">
+      <c r="E14" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="F14" s="214" t="s">
+      <c r="F14" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="G14" s="214" t="s">
+      <c r="G14" s="133" t="s">
         <v>420</v>
       </c>
       <c r="H14" s="47"/>
@@ -11093,13 +11492,13 @@
       <c r="D15" s="45" t="s">
         <v>427</v>
       </c>
-      <c r="E15" s="214" t="s">
+      <c r="E15" s="133" t="s">
         <v>428</v>
       </c>
-      <c r="F15" s="214" t="s">
+      <c r="F15" s="133" t="s">
         <v>429</v>
       </c>
-      <c r="G15" s="214" t="s">
+      <c r="G15" s="133" t="s">
         <v>428</v>
       </c>
       <c r="H15" s="47"/>
@@ -11142,13 +11541,13 @@
       <c r="D16" s="45" t="s">
         <v>427</v>
       </c>
-      <c r="E16" s="214" t="s">
+      <c r="E16" s="133" t="s">
         <v>428</v>
       </c>
-      <c r="F16" s="214" t="s">
+      <c r="F16" s="133" t="s">
         <v>429</v>
       </c>
-      <c r="G16" s="214" t="s">
+      <c r="G16" s="133" t="s">
         <v>428</v>
       </c>
       <c r="H16" s="47"/>
@@ -11185,9 +11584,9 @@
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
       <c r="D17" s="45"/>
-      <c r="E17" s="214"/>
-      <c r="F17" s="214"/>
-      <c r="G17" s="214"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
       <c r="H17" s="47"/>
       <c r="I17" s="47"/>
       <c r="J17" s="47"/>
@@ -11208,9 +11607,9 @@
       <c r="B18" s="45"/>
       <c r="C18" s="45"/>
       <c r="D18" s="45"/>
-      <c r="E18" s="214"/>
-      <c r="F18" s="214"/>
-      <c r="G18" s="214"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
       <c r="H18" s="47"/>
       <c r="I18" s="47"/>
       <c r="J18" s="47"/>
@@ -11227,9 +11626,9 @@
       <c r="B19" s="45"/>
       <c r="C19" s="45"/>
       <c r="D19" s="45"/>
-      <c r="E19" s="214"/>
-      <c r="F19" s="214"/>
-      <c r="G19" s="214"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
       <c r="H19" s="47"/>
       <c r="I19" s="47"/>
       <c r="J19" s="47"/>
@@ -11246,9 +11645,9 @@
       <c r="B20" s="45"/>
       <c r="C20" s="45"/>
       <c r="D20" s="45"/>
-      <c r="E20" s="214"/>
-      <c r="F20" s="214"/>
-      <c r="G20" s="214"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
       <c r="H20" s="47"/>
       <c r="I20" s="47"/>
       <c r="J20" s="47"/>
@@ -11265,9 +11664,9 @@
       <c r="B21" s="47"/>
       <c r="C21" s="47"/>
       <c r="D21" s="45"/>
-      <c r="E21" s="214"/>
-      <c r="F21" s="214"/>
-      <c r="G21" s="214"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
       <c r="H21" s="45"/>
       <c r="I21" s="45"/>
       <c r="J21" s="45"/>
@@ -11284,9 +11683,9 @@
       <c r="B22" s="47"/>
       <c r="C22" s="45"/>
       <c r="D22" s="47"/>
-      <c r="E22" s="216"/>
-      <c r="F22" s="216"/>
-      <c r="G22" s="216"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
       <c r="H22" s="42"/>
       <c r="I22" s="47"/>
       <c r="J22" s="47"/>
@@ -11300,40 +11699,40 @@
       <c r="R22" s="47"/>
     </row>
     <row r="23" spans="2:18" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B23" s="162"/>
-      <c r="C23" s="162"/>
-      <c r="D23" s="162"/>
-      <c r="E23" s="162"/>
-      <c r="F23" s="162"/>
-      <c r="G23" s="162"/>
-      <c r="H23" s="162"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="162"/>
-      <c r="K23" s="162"/>
-      <c r="L23" s="162"/>
-      <c r="M23" s="162"/>
-      <c r="N23" s="162"/>
-      <c r="O23" s="162"/>
-      <c r="P23" s="162"/>
+      <c r="B23" s="190"/>
+      <c r="C23" s="190"/>
+      <c r="D23" s="190"/>
+      <c r="E23" s="190"/>
+      <c r="F23" s="190"/>
+      <c r="G23" s="190"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="190"/>
+      <c r="J23" s="190"/>
+      <c r="K23" s="190"/>
+      <c r="L23" s="190"/>
+      <c r="M23" s="190"/>
+      <c r="N23" s="190"/>
+      <c r="O23" s="190"/>
+      <c r="P23" s="190"/>
     </row>
     <row r="24" spans="2:18" s="50" customFormat="1" ht="24.75" customHeight="1">
-      <c r="B24" s="217" t="s">
+      <c r="B24" s="227" t="s">
         <v>431</v>
       </c>
-      <c r="C24" s="217"/>
-      <c r="D24" s="217"/>
-      <c r="E24" s="217"/>
-      <c r="F24" s="217"/>
-      <c r="G24" s="217"/>
-      <c r="H24" s="217"/>
-      <c r="I24" s="217"/>
-      <c r="J24" s="217"/>
-      <c r="K24" s="217"/>
-      <c r="L24" s="217"/>
-      <c r="M24" s="217"/>
-      <c r="N24" s="217"/>
-      <c r="O24" s="217"/>
-      <c r="P24" s="217"/>
+      <c r="C24" s="227"/>
+      <c r="D24" s="227"/>
+      <c r="E24" s="227"/>
+      <c r="F24" s="227"/>
+      <c r="G24" s="227"/>
+      <c r="H24" s="227"/>
+      <c r="I24" s="227"/>
+      <c r="J24" s="227"/>
+      <c r="K24" s="227"/>
+      <c r="L24" s="227"/>
+      <c r="M24" s="227"/>
+      <c r="N24" s="227"/>
+      <c r="O24" s="227"/>
+      <c r="P24" s="227"/>
     </row>
     <row r="25" spans="2:18" s="50" customFormat="1" ht="10" customHeight="1">
       <c r="B25" s="73"/>
@@ -11348,205 +11747,212 @@
       <c r="K25" s="73"/>
       <c r="L25" s="73"/>
       <c r="M25" s="73"/>
-      <c r="N25" s="218"/>
-      <c r="O25" s="218"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
       <c r="P25" s="73"/>
     </row>
     <row r="26" spans="2:18" ht="24.75" customHeight="1">
-      <c r="B26" s="219" t="s">
+      <c r="B26" s="137" t="s">
         <v>432</v>
       </c>
-      <c r="C26" s="220"/>
-      <c r="D26" s="220"/>
-      <c r="E26" s="221"/>
-      <c r="F26" s="221"/>
-      <c r="G26" s="221"/>
-      <c r="H26" s="220"/>
-      <c r="I26" s="220"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
     </row>
     <row r="27" spans="2:18" ht="24.75" customHeight="1">
-      <c r="B27" s="219" t="s">
+      <c r="B27" s="137" t="s">
         <v>433</v>
       </c>
-      <c r="C27" s="220"/>
-      <c r="D27" s="220"/>
-      <c r="E27" s="221"/>
-      <c r="F27" s="221"/>
-      <c r="G27" s="221"/>
-      <c r="H27" s="220"/>
-      <c r="I27" s="220"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
     </row>
     <row r="29" spans="2:18" ht="24.75" customHeight="1">
-      <c r="B29" s="222" t="s">
+      <c r="B29" s="228" t="s">
         <v>434</v>
       </c>
-      <c r="C29" s="222"/>
-      <c r="D29" s="222"/>
-      <c r="E29" s="222"/>
-      <c r="F29" s="222"/>
-      <c r="G29" s="222"/>
-      <c r="H29" s="222"/>
-      <c r="I29" s="222"/>
-      <c r="J29" s="222"/>
+      <c r="C29" s="228"/>
+      <c r="D29" s="228"/>
+      <c r="E29" s="228"/>
+      <c r="F29" s="228"/>
+      <c r="G29" s="228"/>
+      <c r="H29" s="228"/>
+      <c r="I29" s="228"/>
+      <c r="J29" s="228"/>
     </row>
     <row r="30" spans="2:18" ht="24.75" customHeight="1">
-      <c r="B30" s="223" t="s">
+      <c r="B30" s="229" t="s">
         <v>435</v>
       </c>
-      <c r="C30" s="223"/>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="223"/>
-      <c r="G30" s="223"/>
-      <c r="H30" s="223"/>
-      <c r="I30" s="223"/>
-      <c r="J30" s="223"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="229"/>
+      <c r="G30" s="229"/>
+      <c r="H30" s="229"/>
+      <c r="I30" s="229"/>
+      <c r="J30" s="229"/>
     </row>
     <row r="31" spans="2:18" ht="24.75" customHeight="1">
-      <c r="B31" s="223"/>
-      <c r="C31" s="223"/>
-      <c r="D31" s="223"/>
-      <c r="E31" s="223"/>
-      <c r="F31" s="223"/>
-      <c r="G31" s="223"/>
-      <c r="H31" s="223"/>
-      <c r="I31" s="223"/>
-      <c r="J31" s="223"/>
+      <c r="B31" s="229"/>
+      <c r="C31" s="229"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="229"/>
+      <c r="G31" s="229"/>
+      <c r="H31" s="229"/>
+      <c r="I31" s="229"/>
+      <c r="J31" s="229"/>
     </row>
     <row r="32" spans="2:18" ht="24.75" customHeight="1">
-      <c r="B32" s="223"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="223"/>
-      <c r="I32" s="223"/>
-      <c r="J32" s="223"/>
+      <c r="B32" s="229"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="229"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
+      <c r="G32" s="229"/>
+      <c r="H32" s="229"/>
+      <c r="I32" s="229"/>
+      <c r="J32" s="229"/>
     </row>
     <row r="33" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B33" s="223"/>
-      <c r="C33" s="223"/>
-      <c r="D33" s="223"/>
-      <c r="E33" s="223"/>
-      <c r="F33" s="223"/>
-      <c r="G33" s="223"/>
-      <c r="H33" s="223"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="223"/>
+      <c r="B33" s="229"/>
+      <c r="C33" s="229"/>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
+      <c r="G33" s="229"/>
+      <c r="H33" s="229"/>
+      <c r="I33" s="229"/>
+      <c r="J33" s="229"/>
     </row>
     <row r="34" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B34" s="223"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="223"/>
-      <c r="F34" s="223"/>
-      <c r="G34" s="223"/>
-      <c r="H34" s="223"/>
-      <c r="I34" s="223"/>
-      <c r="J34" s="223"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
     </row>
     <row r="35" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B35" s="223"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="223"/>
-      <c r="F35" s="223"/>
-      <c r="G35" s="223"/>
-      <c r="H35" s="223"/>
-      <c r="I35" s="223"/>
-      <c r="J35" s="223"/>
+      <c r="B35" s="229"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="229"/>
     </row>
     <row r="36" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B36" s="223"/>
-      <c r="C36" s="223"/>
-      <c r="D36" s="223"/>
-      <c r="E36" s="223"/>
-      <c r="F36" s="223"/>
-      <c r="G36" s="223"/>
-      <c r="H36" s="223"/>
-      <c r="I36" s="223"/>
-      <c r="J36" s="223"/>
+      <c r="B36" s="229"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="229"/>
+      <c r="I36" s="229"/>
+      <c r="J36" s="229"/>
     </row>
     <row r="37" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B37" s="223"/>
-      <c r="C37" s="223"/>
-      <c r="D37" s="223"/>
-      <c r="E37" s="223"/>
-      <c r="F37" s="223"/>
-      <c r="G37" s="223"/>
-      <c r="H37" s="223"/>
-      <c r="I37" s="223"/>
-      <c r="J37" s="223"/>
+      <c r="B37" s="229"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="229"/>
+      <c r="I37" s="229"/>
+      <c r="J37" s="229"/>
     </row>
     <row r="38" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B38" s="223"/>
-      <c r="C38" s="223"/>
-      <c r="D38" s="223"/>
-      <c r="E38" s="223"/>
-      <c r="F38" s="223"/>
-      <c r="G38" s="223"/>
-      <c r="H38" s="223"/>
-      <c r="I38" s="223"/>
-      <c r="J38" s="223"/>
+      <c r="B38" s="229"/>
+      <c r="C38" s="229"/>
+      <c r="D38" s="229"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
+      <c r="G38" s="229"/>
+      <c r="H38" s="229"/>
+      <c r="I38" s="229"/>
+      <c r="J38" s="229"/>
     </row>
     <row r="39" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B39" s="223"/>
-      <c r="C39" s="223"/>
-      <c r="D39" s="223"/>
-      <c r="E39" s="223"/>
-      <c r="F39" s="223"/>
-      <c r="G39" s="223"/>
-      <c r="H39" s="223"/>
-      <c r="I39" s="223"/>
-      <c r="J39" s="223"/>
+      <c r="B39" s="229"/>
+      <c r="C39" s="229"/>
+      <c r="D39" s="229"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
+      <c r="G39" s="229"/>
+      <c r="H39" s="229"/>
+      <c r="I39" s="229"/>
+      <c r="J39" s="229"/>
     </row>
     <row r="40" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B40" s="223"/>
-      <c r="C40" s="223"/>
-      <c r="D40" s="223"/>
-      <c r="E40" s="223"/>
-      <c r="F40" s="223"/>
-      <c r="G40" s="223"/>
-      <c r="H40" s="223"/>
-      <c r="I40" s="223"/>
-      <c r="J40" s="223"/>
+      <c r="B40" s="229"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="229"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="229"/>
     </row>
     <row r="41" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B41" s="223"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="223"/>
-      <c r="E41" s="223"/>
-      <c r="F41" s="223"/>
-      <c r="G41" s="223"/>
-      <c r="H41" s="223"/>
-      <c r="I41" s="223"/>
-      <c r="J41" s="223"/>
+      <c r="B41" s="229"/>
+      <c r="C41" s="229"/>
+      <c r="D41" s="229"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
+      <c r="G41" s="229"/>
+      <c r="H41" s="229"/>
+      <c r="I41" s="229"/>
+      <c r="J41" s="229"/>
     </row>
     <row r="42" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B42" s="223"/>
-      <c r="C42" s="223"/>
-      <c r="D42" s="223"/>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="223"/>
-      <c r="H42" s="223"/>
-      <c r="I42" s="223"/>
-      <c r="J42" s="223"/>
+      <c r="B42" s="229"/>
+      <c r="C42" s="229"/>
+      <c r="D42" s="229"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
+      <c r="G42" s="229"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="229"/>
+      <c r="J42" s="229"/>
     </row>
     <row r="43" spans="2:10" ht="24.75" customHeight="1">
-      <c r="B43" s="223"/>
-      <c r="C43" s="223"/>
-      <c r="D43" s="223"/>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="223"/>
-      <c r="H43" s="223"/>
-      <c r="I43" s="223"/>
-      <c r="J43" s="223"/>
+      <c r="B43" s="229"/>
+      <c r="C43" s="229"/>
+      <c r="D43" s="229"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I1:R1"/>
+    <mergeCell ref="I2:R2"/>
+    <mergeCell ref="I3:R3"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="J5:P5"/>
     <mergeCell ref="B23:P23"/>
     <mergeCell ref="B24:P24"/>
     <mergeCell ref="B29:J29"/>
@@ -11557,13 +11963,6 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
-    <mergeCell ref="I1:R1"/>
-    <mergeCell ref="I2:R2"/>
-    <mergeCell ref="I3:R3"/>
-    <mergeCell ref="I4:R4"/>
-    <mergeCell ref="J5:P5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11596,48 +11995,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="44" customHeight="1">
-      <c r="A1" s="200" t="s">
+      <c r="A1" s="158" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="200"/>
-      <c r="K1" s="200"/>
-      <c r="L1" s="200"/>
-      <c r="M1" s="200"/>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="158"/>
+      <c r="R1" s="158"/>
     </row>
     <row r="2" spans="1:18" ht="37" customHeight="1">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="158" t="s">
         <v>294</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="200"/>
-      <c r="N2" s="200"/>
-      <c r="O2" s="200"/>
-      <c r="P2" s="200"/>
-      <c r="Q2" s="200"/>
-      <c r="R2" s="200"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="158"/>
+      <c r="R2" s="158"/>
     </row>
     <row r="3" spans="1:18" ht="29" customHeight="1">
       <c r="A3" s="79" t="s">
@@ -11717,213 +12116,213 @@
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="227" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A5" s="225">
+    <row r="5" spans="1:18" s="143" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A5" s="141">
         <v>1</v>
       </c>
-      <c r="B5" s="226" t="s">
+      <c r="B5" s="142" t="s">
         <v>437</v>
       </c>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="142" t="s">
         <v>438</v>
       </c>
-      <c r="D5" s="225" t="s">
+      <c r="D5" s="141" t="s">
         <v>439</v>
       </c>
-      <c r="E5" s="226" t="s">
+      <c r="E5" s="142" t="s">
         <v>440</v>
       </c>
-      <c r="F5" s="226" t="s">
+      <c r="F5" s="142" t="s">
         <v>441</v>
       </c>
-      <c r="G5" s="226" t="s">
+      <c r="G5" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="226" t="s">
+      <c r="H5" s="142" t="s">
         <v>442</v>
       </c>
-      <c r="I5" s="226" t="s">
+      <c r="I5" s="142" t="s">
         <v>443</v>
       </c>
-      <c r="J5" s="226">
+      <c r="J5" s="142">
         <v>18</v>
       </c>
-      <c r="K5" s="226">
+      <c r="K5" s="142">
         <v>267</v>
       </c>
-      <c r="L5" s="226">
+      <c r="L5" s="142">
         <v>243</v>
       </c>
-      <c r="M5" s="226">
+      <c r="M5" s="142">
         <v>267</v>
       </c>
-      <c r="N5" s="226">
+      <c r="N5" s="142">
         <v>6.5</v>
       </c>
-      <c r="O5" s="225">
+      <c r="O5" s="141">
         <v>200</v>
       </c>
-      <c r="P5" s="225" t="s">
+      <c r="P5" s="141" t="s">
         <v>444</v>
       </c>
-      <c r="Q5" s="226">
+      <c r="Q5" s="142">
         <v>1935.5</v>
       </c>
-      <c r="R5" s="225" t="s">
+      <c r="R5" s="141" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="227" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A6" s="228"/>
-      <c r="B6" s="226" t="s">
+    <row r="6" spans="1:18" s="143" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A6" s="144"/>
+      <c r="B6" s="142" t="s">
         <v>446</v>
       </c>
-      <c r="C6" s="226" t="s">
+      <c r="C6" s="142" t="s">
         <v>447</v>
       </c>
-      <c r="D6" s="225" t="s">
+      <c r="D6" s="141" t="s">
         <v>439</v>
       </c>
-      <c r="E6" s="226" t="s">
+      <c r="E6" s="142" t="s">
         <v>448</v>
       </c>
-      <c r="F6" s="226" t="s">
+      <c r="F6" s="142" t="s">
         <v>441</v>
       </c>
-      <c r="G6" s="226" t="s">
+      <c r="G6" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="226" t="s">
+      <c r="H6" s="142" t="s">
         <v>442</v>
       </c>
-      <c r="I6" s="226" t="s">
+      <c r="I6" s="142" t="s">
         <v>449</v>
       </c>
-      <c r="J6" s="226">
+      <c r="J6" s="142">
         <v>18</v>
       </c>
-      <c r="K6" s="226">
+      <c r="K6" s="142">
         <v>310</v>
       </c>
-      <c r="L6" s="226">
+      <c r="L6" s="142">
         <v>260</v>
       </c>
-      <c r="M6" s="226">
+      <c r="M6" s="142">
         <v>310</v>
       </c>
-      <c r="N6" s="226">
+      <c r="N6" s="142">
         <v>8</v>
       </c>
-      <c r="O6" s="229"/>
-      <c r="P6" s="225" t="s">
+      <c r="O6" s="145"/>
+      <c r="P6" s="141" t="s">
         <v>444</v>
       </c>
-      <c r="Q6" s="226">
+      <c r="Q6" s="142">
         <v>2480</v>
       </c>
-      <c r="R6" s="228"/>
-    </row>
-    <row r="7" spans="1:18" s="227" customFormat="1" ht="14.4" customHeight="1">
-      <c r="A7" s="228"/>
-      <c r="B7" s="226" t="s">
+      <c r="R6" s="144"/>
+    </row>
+    <row r="7" spans="1:18" s="143" customFormat="1" ht="14.4" customHeight="1">
+      <c r="A7" s="144"/>
+      <c r="B7" s="142" t="s">
         <v>446</v>
       </c>
-      <c r="C7" s="226" t="s">
+      <c r="C7" s="142" t="s">
         <v>450</v>
       </c>
-      <c r="D7" s="225" t="s">
+      <c r="D7" s="141" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="226" t="s">
+      <c r="E7" s="142" t="s">
         <v>451</v>
       </c>
-      <c r="F7" s="226" t="s">
+      <c r="F7" s="142" t="s">
         <v>441</v>
       </c>
-      <c r="G7" s="226" t="s">
+      <c r="G7" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="226" t="s">
+      <c r="H7" s="142" t="s">
         <v>442</v>
       </c>
-      <c r="I7" s="226" t="s">
+      <c r="I7" s="142" t="s">
         <v>449</v>
       </c>
-      <c r="J7" s="226">
+      <c r="J7" s="142">
         <v>47</v>
       </c>
-      <c r="K7" s="226">
+      <c r="K7" s="142">
         <v>798</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="142">
         <v>1144</v>
       </c>
-      <c r="M7" s="226">
+      <c r="M7" s="142">
         <v>1144</v>
       </c>
-      <c r="N7" s="226">
+      <c r="N7" s="142">
         <v>6.8</v>
       </c>
-      <c r="O7" s="229"/>
-      <c r="P7" s="225" t="s">
+      <c r="O7" s="145"/>
+      <c r="P7" s="141" t="s">
         <v>444</v>
       </c>
-      <c r="Q7" s="226">
+      <c r="Q7" s="142">
         <v>7779.2</v>
       </c>
-      <c r="R7" s="228"/>
-    </row>
-    <row r="8" spans="1:18" s="227" customFormat="1" ht="15.65" customHeight="1">
-      <c r="A8" s="230"/>
-      <c r="B8" s="226" t="s">
+      <c r="R7" s="144"/>
+    </row>
+    <row r="8" spans="1:18" s="143" customFormat="1" ht="15.65" customHeight="1">
+      <c r="A8" s="146"/>
+      <c r="B8" s="142" t="s">
         <v>452</v>
       </c>
-      <c r="C8" s="226" t="s">
+      <c r="C8" s="142" t="s">
         <v>453</v>
       </c>
-      <c r="D8" s="225" t="s">
+      <c r="D8" s="141" t="s">
         <v>439</v>
       </c>
-      <c r="E8" s="226" t="s">
+      <c r="E8" s="142" t="s">
         <v>454</v>
       </c>
-      <c r="F8" s="226" t="s">
+      <c r="F8" s="142" t="s">
         <v>441</v>
       </c>
-      <c r="G8" s="226" t="s">
+      <c r="G8" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="226" t="s">
+      <c r="H8" s="142" t="s">
         <v>455</v>
       </c>
-      <c r="I8" s="226" t="s">
+      <c r="I8" s="142" t="s">
         <v>449</v>
       </c>
-      <c r="J8" s="226">
+      <c r="J8" s="142">
         <v>17</v>
       </c>
-      <c r="K8" s="226">
+      <c r="K8" s="142">
         <v>151</v>
       </c>
-      <c r="L8" s="226">
+      <c r="L8" s="142">
         <v>273</v>
       </c>
-      <c r="M8" s="226">
+      <c r="M8" s="142">
         <v>273</v>
       </c>
-      <c r="N8" s="226">
+      <c r="N8" s="142">
         <v>7.5</v>
       </c>
-      <c r="O8" s="231">
+      <c r="O8" s="147">
         <v>200</v>
       </c>
-      <c r="P8" s="225" t="s">
+      <c r="P8" s="141" t="s">
         <v>444</v>
       </c>
-      <c r="Q8" s="226">
+      <c r="Q8" s="142">
         <v>2247.5</v>
       </c>
-      <c r="R8" s="230" t="s">
+      <c r="R8" s="146" t="s">
         <v>456</v>
       </c>
     </row>
@@ -11972,18 +12371,18 @@
       <c r="R10" s="109"/>
     </row>
     <row r="11" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A11" s="202" t="s">
+      <c r="A11" s="159" t="s">
         <v>391</v>
       </c>
-      <c r="B11" s="202"/>
-      <c r="C11" s="203"/>
-      <c r="D11" s="203"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="203"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="203"/>
-      <c r="I11" s="204"/>
-      <c r="J11" s="204"/>
+      <c r="B11" s="159"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="161"/>
+      <c r="J11" s="161"/>
       <c r="K11" s="106"/>
       <c r="L11" s="106"/>
       <c r="M11" s="106"/>
@@ -12080,44 +12479,44 @@
       <c r="R15" s="109"/>
     </row>
     <row r="16" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A16" s="189" t="s">
+      <c r="A16" s="149" t="s">
         <v>395</v>
       </c>
-      <c r="B16" s="189"/>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
-      <c r="F16" s="189"/>
-      <c r="G16" s="189"/>
-      <c r="H16" s="189"/>
-      <c r="I16" s="189"/>
-      <c r="J16" s="189"/>
-      <c r="K16" s="189"/>
-      <c r="L16" s="189"/>
-      <c r="M16" s="189"/>
-      <c r="N16" s="189"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="149"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="149"/>
+      <c r="M16" s="149"/>
+      <c r="N16" s="149"/>
       <c r="O16" s="117"/>
       <c r="P16" s="117"/>
       <c r="Q16" s="108"/>
       <c r="R16" s="109"/>
     </row>
     <row r="17" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A17" s="189" t="s">
+      <c r="A17" s="149" t="s">
         <v>396</v>
       </c>
-      <c r="B17" s="189"/>
-      <c r="C17" s="189"/>
-      <c r="D17" s="189"/>
-      <c r="E17" s="189"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="189"/>
-      <c r="H17" s="189"/>
-      <c r="I17" s="189"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="189"/>
-      <c r="L17" s="189"/>
-      <c r="M17" s="189"/>
-      <c r="N17" s="189"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+      <c r="I17" s="149"/>
+      <c r="J17" s="149"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="149"/>
+      <c r="M17" s="149"/>
+      <c r="N17" s="149"/>
       <c r="O17" s="117"/>
       <c r="P17" s="117"/>
       <c r="Q17" s="108"/>
@@ -12144,58 +12543,58 @@
       <c r="R18" s="106"/>
     </row>
     <row r="19" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A19" s="205" t="s">
+      <c r="A19" s="162" t="s">
         <v>397</v>
       </c>
-      <c r="B19" s="205"/>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="205"/>
-      <c r="F19" s="205"/>
-      <c r="G19" s="205"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="205"/>
-      <c r="K19" s="206"/>
-      <c r="L19" s="206"/>
-      <c r="M19" s="206"/>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="206"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
+      <c r="B19" s="162"/>
+      <c r="C19" s="162"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="162"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="162"/>
+      <c r="K19" s="163"/>
+      <c r="L19" s="163"/>
+      <c r="M19" s="163"/>
+      <c r="N19" s="163"/>
+      <c r="O19" s="163"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="163"/>
     </row>
     <row r="20" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A20" s="189" t="s">
+      <c r="A20" s="149" t="s">
         <v>398</v>
       </c>
-      <c r="B20" s="189"/>
-      <c r="C20" s="189"/>
-      <c r="D20" s="189"/>
-      <c r="E20" s="189"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="190"/>
-      <c r="L20" s="190"/>
-      <c r="M20" s="190"/>
-      <c r="N20" s="190"/>
-      <c r="O20" s="190"/>
-      <c r="P20" s="190"/>
-      <c r="Q20" s="190"/>
-      <c r="R20" s="190"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="149"/>
+      <c r="I20" s="149"/>
+      <c r="J20" s="149"/>
+      <c r="K20" s="150"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="150"/>
+      <c r="N20" s="150"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="150"/>
+      <c r="Q20" s="150"/>
+      <c r="R20" s="150"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1">
-      <c r="A21" s="192"/>
-      <c r="B21" s="192"/>
-      <c r="C21" s="193"/>
-      <c r="D21" s="193"/>
-      <c r="E21" s="193"/>
-      <c r="F21" s="193"/>
-      <c r="G21" s="193"/>
-      <c r="H21" s="194"/>
+      <c r="A21" s="151"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="153"/>
       <c r="I21" s="121"/>
       <c r="J21" s="122"/>
       <c r="K21" s="123"/>
@@ -12204,19 +12603,19 @@
       <c r="N21" s="123"/>
       <c r="O21" s="123"/>
       <c r="P21" s="123"/>
-      <c r="Q21" s="232">
+      <c r="Q21" s="148">
         <v>46198</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A22" s="195"/>
-      <c r="B22" s="195"/>
-      <c r="C22" s="196"/>
-      <c r="D22" s="196"/>
-      <c r="E22" s="196"/>
-      <c r="F22" s="196"/>
-      <c r="G22" s="196"/>
-      <c r="H22" s="197"/>
+      <c r="A22" s="154"/>
+      <c r="B22" s="154"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="155"/>
+      <c r="G22" s="155"/>
+      <c r="H22" s="156"/>
       <c r="I22" s="118"/>
       <c r="J22" s="115"/>
       <c r="K22" s="126"/>
@@ -12229,20 +12628,20 @@
       <c r="R22" s="109"/>
     </row>
     <row r="23" spans="1:18" ht="14.4" customHeight="1">
-      <c r="A23" s="198"/>
-      <c r="B23" s="198"/>
-      <c r="C23" s="198"/>
-      <c r="D23" s="198"/>
-      <c r="E23" s="198"/>
-      <c r="F23" s="198"/>
-      <c r="G23" s="198"/>
-      <c r="H23" s="198"/>
-      <c r="I23" s="198"/>
-      <c r="J23" s="198"/>
-      <c r="K23" s="198"/>
-      <c r="L23" s="198"/>
-      <c r="M23" s="198"/>
-      <c r="N23" s="198"/>
+      <c r="A23" s="157"/>
+      <c r="B23" s="157"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="157"/>
+      <c r="E23" s="157"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="157"/>
+      <c r="I23" s="157"/>
+      <c r="J23" s="157"/>
+      <c r="K23" s="157"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="157"/>
+      <c r="N23" s="157"/>
       <c r="O23" s="128"/>
       <c r="P23" s="128"/>
     </row>
@@ -12263,4 +12662,2670 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFC72F6-CDCF-4039-9E44-4B6D1B8A9056}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N80"/>
+  <sheetFormatPr defaultColWidth="10.08203125" defaultRowHeight="24.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="1.9140625" style="48" customWidth="1"/>
+    <col min="2" max="2" width="5.58203125" style="48" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="48" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="48" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" style="48" customWidth="1"/>
+    <col min="7" max="11" width="11.08203125" style="48" customWidth="1"/>
+    <col min="12" max="12" width="11.08203125" style="56" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="48" customWidth="1"/>
+    <col min="14" max="16384" width="10.08203125" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A1" s="164"/>
+      <c r="B1" s="164"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="165" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="29"/>
+    </row>
+    <row r="2" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="29"/>
+    </row>
+    <row r="3" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="166" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="29"/>
+    </row>
+    <row r="4" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A4" s="164"/>
+      <c r="B4" s="164"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="166"/>
+      <c r="F4" s="166"/>
+      <c r="G4" s="166"/>
+      <c r="H4" s="166"/>
+      <c r="I4" s="166"/>
+      <c r="J4" s="166"/>
+      <c r="K4" s="166"/>
+      <c r="L4" s="166"/>
+      <c r="M4" s="29"/>
+    </row>
+    <row r="5" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A5" s="164"/>
+      <c r="B5" s="164"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="167"/>
+      <c r="M5" s="167"/>
+    </row>
+    <row r="6" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A6" s="31"/>
+      <c r="B6" s="168" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168" t="s">
+        <v>460</v>
+      </c>
+      <c r="E6" s="168"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="33"/>
+    </row>
+    <row r="7" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A7" s="31"/>
+      <c r="B7" s="168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="168"/>
+      <c r="D7" s="168" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="168"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="33"/>
+    </row>
+    <row r="8" spans="1:14" ht="24.75" customHeight="1">
+      <c r="A8" s="35"/>
+      <c r="B8" s="168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="168"/>
+      <c r="D8" s="168" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="168"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="36"/>
+    </row>
+    <row r="9" spans="1:14" s="38" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B9" s="168" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="168"/>
+      <c r="D9" s="173" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="173"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="40"/>
+    </row>
+    <row r="10" spans="1:14" s="36" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B10" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="42" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="44" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B11" s="45">
+        <v>1</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>461</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>462</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>463</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="I11" s="45">
+        <v>2</v>
+      </c>
+      <c r="J11" s="45">
+        <v>46</v>
+      </c>
+      <c r="K11" s="45" t="s">
+        <v>465</v>
+      </c>
+      <c r="L11" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M11" s="45">
+        <v>777.4</v>
+      </c>
+      <c r="N11" s="47"/>
+    </row>
+    <row r="12" spans="1:14" ht="24.75" customHeight="1">
+      <c r="B12" s="45">
+        <v>2</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>461</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>462</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>463</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="45" t="s">
+        <v>464</v>
+      </c>
+      <c r="I12" s="45">
+        <v>2</v>
+      </c>
+      <c r="J12" s="45">
+        <v>46</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="45">
+        <v>200</v>
+      </c>
+      <c r="N12" s="47"/>
+    </row>
+    <row r="13" spans="1:14" ht="24.75" customHeight="1">
+      <c r="B13" s="45">
+        <v>3</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>467</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="45" t="s">
+        <v>468</v>
+      </c>
+      <c r="I13" s="45">
+        <v>15</v>
+      </c>
+      <c r="J13" s="45">
+        <v>352</v>
+      </c>
+      <c r="K13" s="45" t="s">
+        <v>469</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M13" s="45">
+        <v>2323.1999999999998</v>
+      </c>
+      <c r="N13" s="47"/>
+    </row>
+    <row r="14" spans="1:14" ht="24.75" customHeight="1">
+      <c r="B14" s="45">
+        <v>4</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>467</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>468</v>
+      </c>
+      <c r="I14" s="45">
+        <v>15</v>
+      </c>
+      <c r="J14" s="45">
+        <v>352</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" s="45">
+        <v>250</v>
+      </c>
+      <c r="N14" s="47"/>
+    </row>
+    <row r="15" spans="1:14" ht="24.75" customHeight="1">
+      <c r="B15" s="45">
+        <v>5</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>471</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>472</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="45">
+        <v>3</v>
+      </c>
+      <c r="J15" s="45">
+        <v>38</v>
+      </c>
+      <c r="K15" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="45">
+        <v>167.2</v>
+      </c>
+      <c r="N15" s="47"/>
+    </row>
+    <row r="16" spans="1:14" ht="24.75" customHeight="1">
+      <c r="B16" s="45">
+        <v>6</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>471</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>472</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="45">
+        <v>3</v>
+      </c>
+      <c r="J16" s="45">
+        <v>38</v>
+      </c>
+      <c r="K16" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M16" s="45">
+        <v>200</v>
+      </c>
+      <c r="N16" s="47"/>
+    </row>
+    <row r="17" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B17" s="45">
+        <v>7</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>473</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>475</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="45">
+        <v>10</v>
+      </c>
+      <c r="J17" s="45">
+        <v>178</v>
+      </c>
+      <c r="K17" s="45" t="s">
+        <v>476</v>
+      </c>
+      <c r="L17" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M17" s="45">
+        <v>1673.2</v>
+      </c>
+      <c r="N17" s="47"/>
+    </row>
+    <row r="18" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B18" s="45">
+        <v>8</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>473</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>475</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="45">
+        <v>10</v>
+      </c>
+      <c r="J18" s="45">
+        <v>178</v>
+      </c>
+      <c r="K18" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L18" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M18" s="45">
+        <v>200</v>
+      </c>
+      <c r="N18" s="47"/>
+    </row>
+    <row r="19" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B19" s="45">
+        <v>9</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>478</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="45">
+        <v>10</v>
+      </c>
+      <c r="J19" s="45">
+        <v>178</v>
+      </c>
+      <c r="K19" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="L19" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M19" s="45">
+        <v>729.8</v>
+      </c>
+      <c r="N19" s="47"/>
+    </row>
+    <row r="20" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B20" s="45">
+        <v>10</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>478</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="45">
+        <v>10</v>
+      </c>
+      <c r="J20" s="45">
+        <v>178</v>
+      </c>
+      <c r="K20" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L20" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M20" s="45">
+        <v>200</v>
+      </c>
+      <c r="N20" s="47"/>
+    </row>
+    <row r="21" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B21" s="45">
+        <v>11</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>479</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>480</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>481</v>
+      </c>
+      <c r="I21" s="45">
+        <v>25</v>
+      </c>
+      <c r="J21" s="45">
+        <v>344</v>
+      </c>
+      <c r="K21" s="45" t="s">
+        <v>482</v>
+      </c>
+      <c r="L21" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21" s="45">
+        <v>1582.4</v>
+      </c>
+      <c r="N21" s="47"/>
+    </row>
+    <row r="22" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B22" s="45">
+        <v>12</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="I22" s="45">
+        <v>70</v>
+      </c>
+      <c r="J22" s="45">
+        <v>975</v>
+      </c>
+      <c r="K22" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="L22" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22" s="45">
+        <v>3510</v>
+      </c>
+      <c r="N22" s="47"/>
+    </row>
+    <row r="23" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B23" s="45">
+        <v>13</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>485</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>486</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="45">
+        <v>128</v>
+      </c>
+      <c r="J23" s="45">
+        <v>2201</v>
+      </c>
+      <c r="K23" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="L23" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M23" s="45">
+        <v>10784.9</v>
+      </c>
+      <c r="N23" s="47"/>
+    </row>
+    <row r="24" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B24" s="45">
+        <v>14</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>485</v>
+      </c>
+      <c r="E24" s="45" t="s">
+        <v>486</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="45">
+        <v>128</v>
+      </c>
+      <c r="J24" s="45">
+        <v>2201</v>
+      </c>
+      <c r="K24" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L24" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M24" s="45">
+        <v>200</v>
+      </c>
+      <c r="N24" s="47"/>
+    </row>
+    <row r="25" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B25" s="45">
+        <v>15</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>487</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>488</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="45">
+        <v>18</v>
+      </c>
+      <c r="J25" s="45">
+        <v>285</v>
+      </c>
+      <c r="K25" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="L25" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25" s="45">
+        <v>1282.5</v>
+      </c>
+      <c r="N25" s="47"/>
+    </row>
+    <row r="26" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B26" s="45">
+        <v>16</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>491</v>
+      </c>
+      <c r="F26" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="I26" s="45">
+        <v>5</v>
+      </c>
+      <c r="J26" s="45">
+        <v>113</v>
+      </c>
+      <c r="K26" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M26" s="45">
+        <v>542.4</v>
+      </c>
+      <c r="N26" s="47"/>
+    </row>
+    <row r="27" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B27" s="45">
+        <v>17</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="E27" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="F27" s="45" t="s">
+        <v>495</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="H27" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="I27" s="45">
+        <v>22</v>
+      </c>
+      <c r="J27" s="45">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="K27" s="45" t="s">
+        <v>497</v>
+      </c>
+      <c r="L27" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M27" s="45">
+        <v>850.2</v>
+      </c>
+      <c r="N27" s="47"/>
+    </row>
+    <row r="28" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B28" s="45">
+        <v>18</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="F28" s="45" t="s">
+        <v>495</v>
+      </c>
+      <c r="G28" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="H28" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="I28" s="45">
+        <v>22</v>
+      </c>
+      <c r="J28" s="45">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="K28" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="L28" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M28" s="45">
+        <v>250</v>
+      </c>
+      <c r="N28" s="47"/>
+    </row>
+    <row r="29" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B29" s="45">
+        <v>19</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="F29" s="45" t="s">
+        <v>495</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="I29" s="45">
+        <v>22</v>
+      </c>
+      <c r="J29" s="45">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="K29" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L29" s="46" t="s">
+        <v>498</v>
+      </c>
+      <c r="M29" s="45">
+        <v>200</v>
+      </c>
+      <c r="N29" s="47"/>
+    </row>
+    <row r="30" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B30" s="45">
+        <v>20</v>
+      </c>
+      <c r="C30" s="45" t="s">
+        <v>492</v>
+      </c>
+      <c r="D30" s="45" t="s">
+        <v>493</v>
+      </c>
+      <c r="E30" s="45" t="s">
+        <v>494</v>
+      </c>
+      <c r="F30" s="45" t="s">
+        <v>495</v>
+      </c>
+      <c r="G30" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="H30" s="45" t="s">
+        <v>496</v>
+      </c>
+      <c r="I30" s="45">
+        <v>22</v>
+      </c>
+      <c r="J30" s="45">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="K30" s="45" t="s">
+        <v>499</v>
+      </c>
+      <c r="L30" s="46" t="s">
+        <v>500</v>
+      </c>
+      <c r="M30" s="45" t="s">
+        <v>501</v>
+      </c>
+      <c r="N30" s="47" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B31" s="45">
+        <v>21</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>418</v>
+      </c>
+      <c r="D31" s="45" t="s">
+        <v>503</v>
+      </c>
+      <c r="E31" s="45" t="s">
+        <v>504</v>
+      </c>
+      <c r="F31" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" s="45">
+        <v>110</v>
+      </c>
+      <c r="J31" s="45">
+        <v>1821</v>
+      </c>
+      <c r="K31" s="45" t="s">
+        <v>505</v>
+      </c>
+      <c r="L31" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M31" s="45">
+        <v>9013.9500000000007</v>
+      </c>
+      <c r="N31" s="47"/>
+    </row>
+    <row r="32" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B32" s="45">
+        <v>22</v>
+      </c>
+      <c r="C32" s="45" t="s">
+        <v>418</v>
+      </c>
+      <c r="D32" s="45" t="s">
+        <v>503</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>504</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I32" s="45">
+        <v>110</v>
+      </c>
+      <c r="J32" s="45">
+        <v>1821</v>
+      </c>
+      <c r="K32" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L32" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M32" s="45">
+        <v>200</v>
+      </c>
+      <c r="N32" s="47"/>
+    </row>
+    <row r="33" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B33" s="45">
+        <v>23</v>
+      </c>
+      <c r="C33" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D33" s="45" t="s">
+        <v>507</v>
+      </c>
+      <c r="E33" s="45" t="s">
+        <v>508</v>
+      </c>
+      <c r="F33" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I33" s="45">
+        <v>104</v>
+      </c>
+      <c r="J33" s="45">
+        <v>1503</v>
+      </c>
+      <c r="K33" s="45" t="s">
+        <v>509</v>
+      </c>
+      <c r="L33" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M33" s="45">
+        <v>6387.75</v>
+      </c>
+      <c r="N33" s="47"/>
+    </row>
+    <row r="34" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B34" s="45">
+        <v>24</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D34" s="45" t="s">
+        <v>507</v>
+      </c>
+      <c r="E34" s="45" t="s">
+        <v>508</v>
+      </c>
+      <c r="F34" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I34" s="45">
+        <v>104</v>
+      </c>
+      <c r="J34" s="45">
+        <v>1503</v>
+      </c>
+      <c r="K34" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L34" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M34" s="45">
+        <v>200</v>
+      </c>
+      <c r="N34" s="47"/>
+    </row>
+    <row r="35" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B35" s="45">
+        <v>25</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>507</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>508</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I35" s="45">
+        <v>104</v>
+      </c>
+      <c r="J35" s="45">
+        <v>1503</v>
+      </c>
+      <c r="K35" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="L35" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="M35" s="45">
+        <v>50</v>
+      </c>
+      <c r="N35" s="47"/>
+    </row>
+    <row r="36" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B36" s="45">
+        <v>26</v>
+      </c>
+      <c r="C36" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D36" s="45" t="s">
+        <v>510</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>511</v>
+      </c>
+      <c r="F36" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="45">
+        <v>44</v>
+      </c>
+      <c r="J36" s="45">
+        <v>657</v>
+      </c>
+      <c r="K36" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="L36" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M36" s="45">
+        <v>2759.4</v>
+      </c>
+      <c r="N36" s="47"/>
+    </row>
+    <row r="37" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B37" s="45">
+        <v>27</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>510</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>511</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="45">
+        <v>44</v>
+      </c>
+      <c r="J37" s="45">
+        <v>657</v>
+      </c>
+      <c r="K37" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L37" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M37" s="45">
+        <v>200</v>
+      </c>
+      <c r="N37" s="47"/>
+    </row>
+    <row r="38" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B38" s="45">
+        <v>28</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>512</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>513</v>
+      </c>
+      <c r="F38" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" s="45">
+        <v>59</v>
+      </c>
+      <c r="J38" s="45">
+        <v>780</v>
+      </c>
+      <c r="K38" s="45" t="s">
+        <v>514</v>
+      </c>
+      <c r="L38" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M38" s="45">
+        <v>3393</v>
+      </c>
+      <c r="N38" s="47"/>
+    </row>
+    <row r="39" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B39" s="45">
+        <v>29</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>506</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>512</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>513</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I39" s="45">
+        <v>59</v>
+      </c>
+      <c r="J39" s="45">
+        <v>780</v>
+      </c>
+      <c r="K39" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L39" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M39" s="45">
+        <v>200</v>
+      </c>
+      <c r="N39" s="47"/>
+    </row>
+    <row r="40" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B40" s="45">
+        <v>30</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D40" s="45" t="s">
+        <v>516</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>517</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="G40" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="I40" s="45">
+        <v>10</v>
+      </c>
+      <c r="J40" s="45">
+        <v>158</v>
+      </c>
+      <c r="K40" s="45" t="s">
+        <v>520</v>
+      </c>
+      <c r="L40" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M40" s="45">
+        <v>932.2</v>
+      </c>
+      <c r="N40" s="47"/>
+    </row>
+    <row r="41" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B41" s="45">
+        <v>31</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>516</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>517</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="I41" s="45">
+        <v>10</v>
+      </c>
+      <c r="J41" s="45">
+        <v>158</v>
+      </c>
+      <c r="K41" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L41" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M41" s="45">
+        <v>200</v>
+      </c>
+      <c r="N41" s="47"/>
+    </row>
+    <row r="42" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B42" s="45">
+        <v>32</v>
+      </c>
+      <c r="C42" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D42" s="45" t="s">
+        <v>521</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>522</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="G42" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="I42" s="45">
+        <v>10</v>
+      </c>
+      <c r="J42" s="45">
+        <v>158</v>
+      </c>
+      <c r="K42" s="45" t="s">
+        <v>525</v>
+      </c>
+      <c r="L42" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M42" s="45">
+        <v>995.4</v>
+      </c>
+      <c r="N42" s="47"/>
+    </row>
+    <row r="43" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B43" s="45">
+        <v>33</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D43" s="45" t="s">
+        <v>521</v>
+      </c>
+      <c r="E43" s="45" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="45" t="s">
+        <v>524</v>
+      </c>
+      <c r="I43" s="45">
+        <v>10</v>
+      </c>
+      <c r="J43" s="45">
+        <v>158</v>
+      </c>
+      <c r="K43" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L43" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M43" s="45">
+        <v>200</v>
+      </c>
+      <c r="N43" s="47"/>
+    </row>
+    <row r="44" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B44" s="45">
+        <v>34</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D44" s="45" t="s">
+        <v>526</v>
+      </c>
+      <c r="E44" s="45" t="s">
+        <v>527</v>
+      </c>
+      <c r="F44" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="G44" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" s="45" t="s">
+        <v>528</v>
+      </c>
+      <c r="I44" s="45">
+        <v>10</v>
+      </c>
+      <c r="J44" s="45">
+        <v>158</v>
+      </c>
+      <c r="K44" s="45" t="s">
+        <v>469</v>
+      </c>
+      <c r="L44" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M44" s="45">
+        <v>1042.8</v>
+      </c>
+      <c r="N44" s="47"/>
+    </row>
+    <row r="45" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B45" s="45">
+        <v>35</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D45" s="45" t="s">
+        <v>526</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>527</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>518</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="45" t="s">
+        <v>528</v>
+      </c>
+      <c r="I45" s="45">
+        <v>10</v>
+      </c>
+      <c r="J45" s="45">
+        <v>158</v>
+      </c>
+      <c r="K45" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L45" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M45" s="45">
+        <v>200</v>
+      </c>
+      <c r="N45" s="47"/>
+    </row>
+    <row r="46" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B46" s="45">
+        <v>36</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>530</v>
+      </c>
+      <c r="F46" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="G46" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I46" s="45">
+        <v>10</v>
+      </c>
+      <c r="J46" s="45">
+        <v>158</v>
+      </c>
+      <c r="K46" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="L46" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M46" s="45">
+        <v>853.2</v>
+      </c>
+      <c r="N46" s="47"/>
+    </row>
+    <row r="47" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B47" s="45">
+        <v>37</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D47" s="45" t="s">
+        <v>529</v>
+      </c>
+      <c r="E47" s="45" t="s">
+        <v>530</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>523</v>
+      </c>
+      <c r="G47" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I47" s="45">
+        <v>10</v>
+      </c>
+      <c r="J47" s="45">
+        <v>158</v>
+      </c>
+      <c r="K47" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L47" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M47" s="45">
+        <v>200</v>
+      </c>
+      <c r="N47" s="47"/>
+    </row>
+    <row r="48" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B48" s="45">
+        <v>38</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D48" s="45" t="s">
+        <v>531</v>
+      </c>
+      <c r="E48" s="45" t="s">
+        <v>532</v>
+      </c>
+      <c r="F48" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H48" s="45" t="s">
+        <v>533</v>
+      </c>
+      <c r="I48" s="45">
+        <v>10</v>
+      </c>
+      <c r="J48" s="45">
+        <v>158</v>
+      </c>
+      <c r="K48" s="45" t="s">
+        <v>534</v>
+      </c>
+      <c r="L48" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M48" s="45">
+        <v>805.8</v>
+      </c>
+      <c r="N48" s="47"/>
+    </row>
+    <row r="49" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B49" s="45">
+        <v>39</v>
+      </c>
+      <c r="C49" s="45" t="s">
+        <v>515</v>
+      </c>
+      <c r="D49" s="45" t="s">
+        <v>531</v>
+      </c>
+      <c r="E49" s="45" t="s">
+        <v>532</v>
+      </c>
+      <c r="F49" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H49" s="45" t="s">
+        <v>533</v>
+      </c>
+      <c r="I49" s="45">
+        <v>10</v>
+      </c>
+      <c r="J49" s="45">
+        <v>158</v>
+      </c>
+      <c r="K49" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L49" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M49" s="45">
+        <v>200</v>
+      </c>
+      <c r="N49" s="47"/>
+    </row>
+    <row r="50" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B50" s="45">
+        <v>40</v>
+      </c>
+      <c r="C50" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D50" s="45" t="s">
+        <v>535</v>
+      </c>
+      <c r="E50" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="F50" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I50" s="45">
+        <v>45</v>
+      </c>
+      <c r="J50" s="45">
+        <v>680</v>
+      </c>
+      <c r="K50" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="L50" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M50" s="45">
+        <v>3536</v>
+      </c>
+      <c r="N50" s="47"/>
+    </row>
+    <row r="51" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B51" s="45">
+        <v>41</v>
+      </c>
+      <c r="C51" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D51" s="45" t="s">
+        <v>535</v>
+      </c>
+      <c r="E51" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I51" s="45">
+        <v>45</v>
+      </c>
+      <c r="J51" s="45">
+        <v>680</v>
+      </c>
+      <c r="K51" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L51" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M51" s="45">
+        <v>200</v>
+      </c>
+      <c r="N51" s="47"/>
+    </row>
+    <row r="52" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B52" s="45">
+        <v>42</v>
+      </c>
+      <c r="C52" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D52" s="45" t="s">
+        <v>535</v>
+      </c>
+      <c r="E52" s="45" t="s">
+        <v>536</v>
+      </c>
+      <c r="F52" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G52" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I52" s="45">
+        <v>45</v>
+      </c>
+      <c r="J52" s="45">
+        <v>680</v>
+      </c>
+      <c r="K52" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="L52" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="M52" s="45">
+        <v>50</v>
+      </c>
+      <c r="N52" s="47"/>
+    </row>
+    <row r="53" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B53" s="45">
+        <v>43</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D53" s="45" t="s">
+        <v>537</v>
+      </c>
+      <c r="E53" s="45" t="s">
+        <v>538</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I53" s="45">
+        <v>10</v>
+      </c>
+      <c r="J53" s="45">
+        <v>208</v>
+      </c>
+      <c r="K53" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="L53" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M53" s="45">
+        <v>977.6</v>
+      </c>
+      <c r="N53" s="47"/>
+    </row>
+    <row r="54" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B54" s="45">
+        <v>44</v>
+      </c>
+      <c r="C54" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="D54" s="45" t="s">
+        <v>537</v>
+      </c>
+      <c r="E54" s="45" t="s">
+        <v>538</v>
+      </c>
+      <c r="F54" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54" s="45">
+        <v>10</v>
+      </c>
+      <c r="J54" s="45">
+        <v>208</v>
+      </c>
+      <c r="K54" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L54" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M54" s="45">
+        <v>200</v>
+      </c>
+      <c r="N54" s="47"/>
+    </row>
+    <row r="55" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B55" s="45">
+        <v>45</v>
+      </c>
+      <c r="C55" s="45" t="s">
+        <v>539</v>
+      </c>
+      <c r="D55" s="45" t="s">
+        <v>540</v>
+      </c>
+      <c r="E55" s="45" t="s">
+        <v>541</v>
+      </c>
+      <c r="F55" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I55" s="45">
+        <v>46</v>
+      </c>
+      <c r="J55" s="45">
+        <v>640</v>
+      </c>
+      <c r="K55" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="L55" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M55" s="45">
+        <v>2560</v>
+      </c>
+      <c r="N55" s="47"/>
+    </row>
+    <row r="56" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B56" s="45">
+        <v>46</v>
+      </c>
+      <c r="C56" s="45" t="s">
+        <v>539</v>
+      </c>
+      <c r="D56" s="45" t="s">
+        <v>542</v>
+      </c>
+      <c r="E56" s="45" t="s">
+        <v>543</v>
+      </c>
+      <c r="F56" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I56" s="45">
+        <v>10</v>
+      </c>
+      <c r="J56" s="45">
+        <v>139</v>
+      </c>
+      <c r="K56" s="45" t="s">
+        <v>489</v>
+      </c>
+      <c r="L56" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M56" s="45">
+        <v>625.5</v>
+      </c>
+      <c r="N56" s="47"/>
+    </row>
+    <row r="57" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B57" s="45">
+        <v>47</v>
+      </c>
+      <c r="C57" s="45" t="s">
+        <v>544</v>
+      </c>
+      <c r="D57" s="45" t="s">
+        <v>545</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>546</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57" s="45" t="s">
+        <v>547</v>
+      </c>
+      <c r="I57" s="45">
+        <v>5</v>
+      </c>
+      <c r="J57" s="45">
+        <v>68</v>
+      </c>
+      <c r="K57" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="L57" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M57" s="45">
+        <v>367.2</v>
+      </c>
+      <c r="N57" s="47"/>
+    </row>
+    <row r="58" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B58" s="45">
+        <v>48</v>
+      </c>
+      <c r="C58" s="45" t="s">
+        <v>544</v>
+      </c>
+      <c r="D58" s="45" t="s">
+        <v>545</v>
+      </c>
+      <c r="E58" s="45" t="s">
+        <v>546</v>
+      </c>
+      <c r="F58" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G58" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H58" s="45" t="s">
+        <v>547</v>
+      </c>
+      <c r="I58" s="45">
+        <v>5</v>
+      </c>
+      <c r="J58" s="45">
+        <v>68</v>
+      </c>
+      <c r="K58" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L58" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M58" s="45">
+        <v>200</v>
+      </c>
+      <c r="N58" s="47"/>
+    </row>
+    <row r="59" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B59" s="45">
+        <v>49</v>
+      </c>
+      <c r="C59" s="45" t="s">
+        <v>544</v>
+      </c>
+      <c r="D59" s="45" t="s">
+        <v>548</v>
+      </c>
+      <c r="E59" s="45" t="s">
+        <v>549</v>
+      </c>
+      <c r="F59" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59" s="45" t="s">
+        <v>547</v>
+      </c>
+      <c r="I59" s="45">
+        <v>12</v>
+      </c>
+      <c r="J59" s="45">
+        <v>172</v>
+      </c>
+      <c r="K59" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="L59" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M59" s="45">
+        <v>928.8</v>
+      </c>
+      <c r="N59" s="47"/>
+    </row>
+    <row r="60" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B60" s="45">
+        <v>50</v>
+      </c>
+      <c r="C60" s="45" t="s">
+        <v>544</v>
+      </c>
+      <c r="D60" s="45" t="s">
+        <v>548</v>
+      </c>
+      <c r="E60" s="45" t="s">
+        <v>549</v>
+      </c>
+      <c r="F60" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G60" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" s="45" t="s">
+        <v>547</v>
+      </c>
+      <c r="I60" s="45">
+        <v>12</v>
+      </c>
+      <c r="J60" s="45">
+        <v>172</v>
+      </c>
+      <c r="K60" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L60" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M60" s="45">
+        <v>200</v>
+      </c>
+      <c r="N60" s="47"/>
+    </row>
+    <row r="61" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B61" s="45">
+        <v>51</v>
+      </c>
+      <c r="C61" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61" s="45" t="s">
+        <v>550</v>
+      </c>
+      <c r="E61" s="45" t="s">
+        <v>551</v>
+      </c>
+      <c r="F61" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>547</v>
+      </c>
+      <c r="I61" s="45">
+        <v>134</v>
+      </c>
+      <c r="J61" s="45">
+        <v>2114</v>
+      </c>
+      <c r="K61" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="L61" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M61" s="45">
+        <v>11415.6</v>
+      </c>
+      <c r="N61" s="47"/>
+    </row>
+    <row r="62" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B62" s="45">
+        <v>52</v>
+      </c>
+      <c r="C62" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D62" s="45" t="s">
+        <v>552</v>
+      </c>
+      <c r="E62" s="45" t="s">
+        <v>553</v>
+      </c>
+      <c r="F62" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I62" s="45">
+        <v>7</v>
+      </c>
+      <c r="J62" s="45">
+        <v>95</v>
+      </c>
+      <c r="K62" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="L62" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M62" s="45">
+        <v>380</v>
+      </c>
+      <c r="N62" s="47"/>
+    </row>
+    <row r="63" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B63" s="45">
+        <v>53</v>
+      </c>
+      <c r="C63" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" s="45" t="s">
+        <v>554</v>
+      </c>
+      <c r="E63" s="45" t="s">
+        <v>555</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" s="45">
+        <v>13</v>
+      </c>
+      <c r="J63" s="45">
+        <v>296</v>
+      </c>
+      <c r="K63" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="L63" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M63" s="45">
+        <v>1480</v>
+      </c>
+      <c r="N63" s="47"/>
+    </row>
+    <row r="64" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B64" s="45">
+        <v>54</v>
+      </c>
+      <c r="C64" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D64" s="45" t="s">
+        <v>556</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>557</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H64" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="I64" s="45">
+        <v>15</v>
+      </c>
+      <c r="J64" s="45">
+        <v>206</v>
+      </c>
+      <c r="K64" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="L64" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M64" s="45">
+        <v>824</v>
+      </c>
+      <c r="N64" s="47"/>
+    </row>
+    <row r="65" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B65" s="45">
+        <v>55</v>
+      </c>
+      <c r="C65" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D65" s="45" t="s">
+        <v>558</v>
+      </c>
+      <c r="E65" s="45" t="s">
+        <v>559</v>
+      </c>
+      <c r="F65" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I65" s="45">
+        <v>46</v>
+      </c>
+      <c r="J65" s="45">
+        <v>636</v>
+      </c>
+      <c r="K65" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="L65" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M65" s="45">
+        <v>3180</v>
+      </c>
+      <c r="N65" s="47"/>
+    </row>
+    <row r="66" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B66" s="45">
+        <v>56</v>
+      </c>
+      <c r="C66" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D66" s="45" t="s">
+        <v>560</v>
+      </c>
+      <c r="E66" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="F66" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G66" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H66" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="I66" s="45">
+        <v>21</v>
+      </c>
+      <c r="J66" s="45">
+        <v>322</v>
+      </c>
+      <c r="K66" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="L66" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="M66" s="45">
+        <v>1610</v>
+      </c>
+      <c r="N66" s="47"/>
+    </row>
+    <row r="67" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B67" s="45">
+        <v>57</v>
+      </c>
+      <c r="C67" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="D67" s="45" t="s">
+        <v>560</v>
+      </c>
+      <c r="E67" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="F67" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" s="45">
+        <v>21</v>
+      </c>
+      <c r="J67" s="45">
+        <v>322</v>
+      </c>
+      <c r="K67" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="L67" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="M67" s="45">
+        <v>200</v>
+      </c>
+      <c r="N67" s="47"/>
+    </row>
+    <row r="68" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B68" s="45"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="45"/>
+      <c r="J68" s="45"/>
+      <c r="K68" s="45"/>
+      <c r="L68" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="M68" s="45" t="s">
+        <v>562</v>
+      </c>
+      <c r="N68" s="47"/>
+    </row>
+    <row r="69" spans="2:14" s="44" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="45"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="47"/>
+      <c r="L69" s="49"/>
+      <c r="M69" s="47"/>
+      <c r="N69" s="47"/>
+    </row>
+    <row r="70" spans="2:14" s="44" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B70" s="47"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
+      <c r="L70" s="49"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="47"/>
+    </row>
+    <row r="71" spans="2:14" s="50" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B71" s="174"/>
+      <c r="C71" s="174"/>
+      <c r="D71" s="174"/>
+      <c r="E71" s="174"/>
+      <c r="F71" s="174"/>
+      <c r="G71" s="174"/>
+      <c r="H71" s="174"/>
+      <c r="I71" s="174"/>
+      <c r="J71" s="174"/>
+      <c r="K71" s="174"/>
+      <c r="L71" s="174"/>
+      <c r="M71" s="174"/>
+    </row>
+    <row r="72" spans="2:14" s="50" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B72" s="175"/>
+      <c r="C72" s="175"/>
+      <c r="D72" s="175"/>
+      <c r="E72" s="175"/>
+      <c r="F72" s="175"/>
+      <c r="G72" s="175"/>
+      <c r="H72" s="175"/>
+      <c r="I72" s="175"/>
+      <c r="J72" s="175"/>
+      <c r="K72" s="175"/>
+      <c r="L72" s="175"/>
+      <c r="M72" s="175"/>
+    </row>
+    <row r="73" spans="2:14" s="50" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B73" s="175" t="s">
+        <v>160</v>
+      </c>
+      <c r="C73" s="175"/>
+      <c r="D73" s="175"/>
+      <c r="E73" s="175"/>
+      <c r="F73" s="175"/>
+      <c r="G73" s="175"/>
+      <c r="H73" s="175"/>
+      <c r="I73" s="175"/>
+      <c r="J73" s="175"/>
+      <c r="K73" s="175"/>
+      <c r="L73" s="175"/>
+      <c r="M73" s="175"/>
+    </row>
+    <row r="74" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B74" s="176" t="s">
+        <v>161</v>
+      </c>
+      <c r="C74" s="176"/>
+      <c r="D74" s="176"/>
+      <c r="E74" s="176"/>
+      <c r="F74" s="51"/>
+      <c r="G74" s="51"/>
+      <c r="H74" s="51"/>
+      <c r="I74" s="51"/>
+      <c r="J74" s="51"/>
+      <c r="K74" s="52"/>
+      <c r="L74" s="53"/>
+      <c r="M74" s="51"/>
+    </row>
+    <row r="75" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B75" s="169" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" s="170"/>
+      <c r="D75" s="170"/>
+      <c r="E75" s="171"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
+      <c r="J75" s="51"/>
+      <c r="K75" s="51"/>
+      <c r="L75" s="53"/>
+      <c r="M75" s="51"/>
+    </row>
+    <row r="76" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B76" s="169" t="s">
+        <v>163</v>
+      </c>
+      <c r="C76" s="170"/>
+      <c r="D76" s="170"/>
+      <c r="E76" s="171"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
+      <c r="J76" s="51"/>
+      <c r="K76" s="51"/>
+      <c r="L76" s="53"/>
+      <c r="M76" s="51"/>
+    </row>
+    <row r="77" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B77" s="51"/>
+      <c r="C77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="51"/>
+      <c r="G77" s="51"/>
+      <c r="H77" s="51"/>
+      <c r="I77" s="51"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="51"/>
+      <c r="L77" s="53"/>
+      <c r="M77" s="51"/>
+    </row>
+    <row r="78" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B78" s="172" t="s">
+        <v>164</v>
+      </c>
+      <c r="C78" s="172"/>
+      <c r="D78" s="172"/>
+      <c r="E78" s="172"/>
+      <c r="F78" s="172"/>
+      <c r="G78" s="172"/>
+      <c r="H78" s="172"/>
+      <c r="I78" s="172"/>
+      <c r="J78" s="54"/>
+      <c r="K78" s="54"/>
+      <c r="L78" s="55"/>
+      <c r="M78" s="54"/>
+    </row>
+    <row r="79" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B79" s="172"/>
+      <c r="C79" s="172"/>
+      <c r="D79" s="172"/>
+      <c r="E79" s="172"/>
+      <c r="F79" s="172"/>
+      <c r="G79" s="172"/>
+      <c r="H79" s="172"/>
+      <c r="I79" s="172"/>
+      <c r="J79" s="54"/>
+      <c r="K79" s="54"/>
+      <c r="L79" s="55"/>
+      <c r="M79" s="54"/>
+    </row>
+    <row r="80" spans="2:14" ht="24.75" customHeight="1">
+      <c r="B80" s="172"/>
+      <c r="C80" s="172"/>
+      <c r="D80" s="172"/>
+      <c r="E80" s="172"/>
+      <c r="F80" s="172"/>
+      <c r="G80" s="172"/>
+      <c r="H80" s="172"/>
+      <c r="I80" s="172"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B78:I80"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B71:M71"/>
+    <mergeCell ref="B72:M72"/>
+    <mergeCell ref="B73:M73"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:L2"/>
+    <mergeCell ref="E3:L4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="I5:M5"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>